--- a/experiment/SwinT2_bestx4/results_HUTCN_SwinT2_bestx4.xlsx
+++ b/experiment/SwinT2_bestx4/results_HUTCN_SwinT2_bestx4.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E221"/>
+  <dimension ref="A1:E411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,10 +477,10 @@
         <v>0.000328</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01484</v>
+        <v>0.01023</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01484</v>
+        <v>0.01023</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>28.043</v>
@@ -494,12 +494,12 @@
         <v>0.000328</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00338</v>
+        <v>0.00336</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00338</v>
-      </c>
-      <c r="E3" s="2" t="n">
+        <v>0.00336</v>
+      </c>
+      <c r="E3" t="n">
         <v>27.921</v>
       </c>
     </row>
@@ -511,10 +511,10 @@
         <v>0.000328</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0032</v>
+        <v>0.00325</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0032</v>
+        <v>0.00325</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>29.586</v>
@@ -528,10 +528,10 @@
         <v>0.000328</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00319</v>
+        <v>0.00318</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00319</v>
+        <v>0.00318</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>30.052</v>
@@ -545,10 +545,10 @@
         <v>0.000328</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003105000000000001</v>
+        <v>0.00298</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003105000000000001</v>
+        <v>0.00298</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>30.426</v>
@@ -562,10 +562,10 @@
         <v>0.000328</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00308</v>
+        <v>0.00297</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00308</v>
+        <v>0.00297</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>30.674</v>
@@ -579,10 +579,10 @@
         <v>0.000328</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002995</v>
+        <v>0.00278</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002995</v>
+        <v>0.00278</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>30.733</v>
@@ -596,10 +596,10 @@
         <v>0.000328</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003075</v>
+        <v>0.00288</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003075</v>
+        <v>0.00288</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>30.825</v>
@@ -613,12 +613,12 @@
         <v>0.000327</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00304</v>
+        <v>0.00287</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00304</v>
-      </c>
-      <c r="E10" s="2" t="n">
+        <v>0.00287</v>
+      </c>
+      <c r="E10" t="n">
         <v>30.54</v>
       </c>
     </row>
@@ -630,12 +630,12 @@
         <v>0.000327</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002949999999999999</v>
+        <v>0.00284</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002949999999999999</v>
-      </c>
-      <c r="E11" s="2" t="n">
+        <v>0.00284</v>
+      </c>
+      <c r="E11" t="n">
         <v>30.784</v>
       </c>
     </row>
@@ -647,10 +647,10 @@
         <v>0.000327</v>
       </c>
       <c r="C12" t="n">
-        <v>0.00289</v>
+        <v>0.0027</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00289</v>
+        <v>0.0027</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>30.872</v>
@@ -664,10 +664,10 @@
         <v>0.000326</v>
       </c>
       <c r="C13" t="n">
-        <v>0.002955</v>
+        <v>0.00279</v>
       </c>
       <c r="D13" t="n">
-        <v>0.002955</v>
+        <v>0.00279</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>31.028</v>
@@ -681,10 +681,10 @@
         <v>0.000326</v>
       </c>
       <c r="C14" t="n">
-        <v>0.002894999999999999</v>
+        <v>0.00278</v>
       </c>
       <c r="D14" t="n">
-        <v>0.002894999999999999</v>
+        <v>0.00278</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>31.165</v>
@@ -698,10 +698,10 @@
         <v>0.000326</v>
       </c>
       <c r="C15" t="n">
-        <v>0.002949999999999999</v>
+        <v>0.0028</v>
       </c>
       <c r="D15" t="n">
-        <v>0.002949999999999999</v>
+        <v>0.0028</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>31.232</v>
@@ -715,10 +715,10 @@
         <v>0.000325</v>
       </c>
       <c r="C16" t="n">
-        <v>0.00292</v>
+        <v>0.002730000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00292</v>
+        <v>0.002730000000000001</v>
       </c>
       <c r="E16" t="n">
         <v>31.079</v>
@@ -732,10 +732,10 @@
         <v>0.000325</v>
       </c>
       <c r="C17" t="n">
-        <v>0.002875</v>
+        <v>0.002690000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.002875</v>
+        <v>0.002690000000000001</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>31.281</v>
@@ -749,12 +749,12 @@
         <v>0.000324</v>
       </c>
       <c r="C18" t="n">
-        <v>0.00284</v>
+        <v>0.002690000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00284</v>
-      </c>
-      <c r="E18" s="2" t="n">
+        <v>0.002690000000000001</v>
+      </c>
+      <c r="E18" t="n">
         <v>31.259</v>
       </c>
     </row>
@@ -766,12 +766,12 @@
         <v>0.000324</v>
       </c>
       <c r="C19" t="n">
-        <v>0.002850000000000001</v>
+        <v>0.002680000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>0.002850000000000001</v>
-      </c>
-      <c r="E19" s="2" t="n">
+        <v>0.002680000000000001</v>
+      </c>
+      <c r="E19" t="n">
         <v>31.161</v>
       </c>
     </row>
@@ -783,10 +783,10 @@
         <v>0.000323</v>
       </c>
       <c r="C20" t="n">
-        <v>0.002785</v>
+        <v>0.0027</v>
       </c>
       <c r="D20" t="n">
-        <v>0.002785</v>
+        <v>0.0027</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>31.406</v>
@@ -800,10 +800,10 @@
         <v>0.000322</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00277</v>
+        <v>0.0026</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00277</v>
+        <v>0.0026</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>31.412</v>
@@ -817,10 +817,10 @@
         <v>0.000322</v>
       </c>
       <c r="C22" t="n">
-        <v>0.002795</v>
+        <v>0.002599999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.002795</v>
+        <v>0.002599999999999999</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>31.436</v>
@@ -834,10 +834,10 @@
         <v>0.000321</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00281</v>
+        <v>0.002690000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00281</v>
+        <v>0.002690000000000001</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>31.5</v>
@@ -851,12 +851,12 @@
         <v>0.00032</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0028</v>
+        <v>0.00266</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="E24" s="2" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="E24" t="n">
         <v>31.459</v>
       </c>
     </row>
@@ -868,12 +868,12 @@
         <v>0.00032</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0028</v>
+        <v>0.00269</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="E25" s="2" t="n">
+        <v>0.00269</v>
+      </c>
+      <c r="E25" t="n">
         <v>31.322</v>
       </c>
     </row>
@@ -885,12 +885,12 @@
         <v>0.000319</v>
       </c>
       <c r="C26" t="n">
-        <v>0.002715</v>
+        <v>0.00266</v>
       </c>
       <c r="D26" t="n">
-        <v>0.002715</v>
-      </c>
-      <c r="E26" s="2" t="n">
+        <v>0.00266</v>
+      </c>
+      <c r="E26" t="n">
         <v>31.465</v>
       </c>
     </row>
@@ -902,10 +902,10 @@
         <v>0.000318</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0027</v>
+        <v>0.00264</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0027</v>
+        <v>0.00264</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>31.513</v>
@@ -919,12 +919,12 @@
         <v>0.000317</v>
       </c>
       <c r="C28" t="n">
-        <v>0.002735</v>
+        <v>0.00267</v>
       </c>
       <c r="D28" t="n">
-        <v>0.002735</v>
-      </c>
-      <c r="E28" s="2" t="n">
+        <v>0.00267</v>
+      </c>
+      <c r="E28" t="n">
         <v>31.362</v>
       </c>
     </row>
@@ -936,10 +936,10 @@
         <v>0.000316</v>
       </c>
       <c r="C29" t="n">
-        <v>0.002745</v>
+        <v>0.00265</v>
       </c>
       <c r="D29" t="n">
-        <v>0.002745</v>
+        <v>0.00265</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>31.562</v>
@@ -953,12 +953,12 @@
         <v>0.000316</v>
       </c>
       <c r="C30" t="n">
-        <v>0.00275</v>
+        <v>0.00268</v>
       </c>
       <c r="D30" t="n">
-        <v>0.00275</v>
-      </c>
-      <c r="E30" s="2" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="E30" t="n">
         <v>31.357</v>
       </c>
     </row>
@@ -970,10 +970,10 @@
         <v>0.000315</v>
       </c>
       <c r="C31" t="n">
-        <v>0.002775000000000001</v>
+        <v>0.00271</v>
       </c>
       <c r="D31" t="n">
-        <v>0.002775000000000001</v>
+        <v>0.00271</v>
       </c>
       <c r="E31" t="n">
         <v>31.542</v>
@@ -987,10 +987,10 @@
         <v>0.000314</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0027</v>
+        <v>0.002599999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0027</v>
+        <v>0.002599999999999999</v>
       </c>
       <c r="E32" t="n">
         <v>31.47</v>
@@ -1004,12 +1004,12 @@
         <v>0.000313</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0027</v>
+        <v>0.00265</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="E33" s="2" t="n">
+        <v>0.00265</v>
+      </c>
+      <c r="E33" t="n">
         <v>31.432</v>
       </c>
     </row>
@@ -1021,10 +1021,10 @@
         <v>0.000312</v>
       </c>
       <c r="C34" t="n">
-        <v>0.002674999999999999</v>
+        <v>0.002599999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>0.002674999999999999</v>
+        <v>0.002599999999999999</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>31.612</v>
@@ -1038,10 +1038,10 @@
         <v>0.000311</v>
       </c>
       <c r="C35" t="n">
-        <v>0.002694999999999999</v>
+        <v>0.00261</v>
       </c>
       <c r="D35" t="n">
-        <v>0.002694999999999999</v>
+        <v>0.00261</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>31.625</v>
@@ -1055,10 +1055,10 @@
         <v>0.00031</v>
       </c>
       <c r="C36" t="n">
-        <v>0.002690000000000001</v>
+        <v>0.0027</v>
       </c>
       <c r="D36" t="n">
-        <v>0.002690000000000001</v>
+        <v>0.0027</v>
       </c>
       <c r="E36" t="n">
         <v>31.604</v>
@@ -1072,10 +1072,10 @@
         <v>0.000308</v>
       </c>
       <c r="C37" t="n">
-        <v>0.00265</v>
+        <v>0.002599999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>0.00265</v>
+        <v>0.002599999999999999</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>31.7</v>
@@ -1089,10 +1089,10 @@
         <v>0.000307</v>
       </c>
       <c r="C38" t="n">
-        <v>0.002605</v>
+        <v>0.00254</v>
       </c>
       <c r="D38" t="n">
-        <v>0.002605</v>
+        <v>0.00254</v>
       </c>
       <c r="E38" t="n">
         <v>31.659</v>
@@ -1106,12 +1106,12 @@
         <v>0.000306</v>
       </c>
       <c r="C39" t="n">
-        <v>0.002705</v>
+        <v>0.00261</v>
       </c>
       <c r="D39" t="n">
-        <v>0.002705</v>
-      </c>
-      <c r="E39" s="2" t="n">
+        <v>0.00261</v>
+      </c>
+      <c r="E39" t="n">
         <v>31.657</v>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
         <v>0.000305</v>
       </c>
       <c r="C40" t="n">
-        <v>0.00263</v>
+        <v>0.00261</v>
       </c>
       <c r="D40" t="n">
-        <v>0.00263</v>
-      </c>
-      <c r="E40" s="2" t="n">
+        <v>0.00261</v>
+      </c>
+      <c r="E40" t="n">
         <v>31.697</v>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
         <v>0.000304</v>
       </c>
       <c r="C41" t="n">
-        <v>0.00265</v>
+        <v>0.00259</v>
       </c>
       <c r="D41" t="n">
-        <v>0.00265</v>
-      </c>
-      <c r="E41" s="2" t="n">
+        <v>0.00259</v>
+      </c>
+      <c r="E41" t="n">
         <v>31.578</v>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
         <v>0.000302</v>
       </c>
       <c r="C42" t="n">
-        <v>0.002605000000000001</v>
+        <v>0.00251</v>
       </c>
       <c r="D42" t="n">
-        <v>0.002605000000000001</v>
-      </c>
-      <c r="E42" s="2" t="n">
+        <v>0.00251</v>
+      </c>
+      <c r="E42" t="n">
         <v>31.677</v>
       </c>
     </row>
@@ -1174,10 +1174,10 @@
         <v>0.000301</v>
       </c>
       <c r="C43" t="n">
-        <v>0.002655</v>
+        <v>0.00264</v>
       </c>
       <c r="D43" t="n">
-        <v>0.002655</v>
+        <v>0.00264</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>31.722</v>
@@ -1191,10 +1191,10 @@
         <v>0.0003</v>
       </c>
       <c r="C44" t="n">
-        <v>0.00261</v>
+        <v>0.0025</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00261</v>
+        <v>0.0025</v>
       </c>
       <c r="E44" t="n">
         <v>31.662</v>
@@ -1208,10 +1208,10 @@
         <v>0.000299</v>
       </c>
       <c r="C45" t="n">
-        <v>0.002674999999999999</v>
+        <v>0.00261</v>
       </c>
       <c r="D45" t="n">
-        <v>0.002674999999999999</v>
+        <v>0.00261</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>31.742</v>
@@ -1225,12 +1225,12 @@
         <v>0.000297</v>
       </c>
       <c r="C46" t="n">
-        <v>0.002565</v>
+        <v>0.00249</v>
       </c>
       <c r="D46" t="n">
-        <v>0.002565</v>
-      </c>
-      <c r="E46" s="2" t="n">
+        <v>0.00249</v>
+      </c>
+      <c r="E46" t="n">
         <v>31.566</v>
       </c>
     </row>
@@ -1242,10 +1242,10 @@
         <v>0.000296</v>
       </c>
       <c r="C47" t="n">
-        <v>0.00265</v>
+        <v>0.002599999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00265</v>
+        <v>0.002599999999999999</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>31.752</v>
@@ -1259,10 +1259,10 @@
         <v>0.000294</v>
       </c>
       <c r="C48" t="n">
-        <v>0.002634999999999999</v>
+        <v>0.00257</v>
       </c>
       <c r="D48" t="n">
-        <v>0.002634999999999999</v>
+        <v>0.00257</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>31.78</v>
@@ -1276,12 +1276,12 @@
         <v>0.000293</v>
       </c>
       <c r="C49" t="n">
-        <v>0.00265</v>
+        <v>0.00255</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00265</v>
-      </c>
-      <c r="E49" s="2" t="n">
+        <v>0.00255</v>
+      </c>
+      <c r="E49" t="n">
         <v>31.745</v>
       </c>
     </row>
@@ -1293,10 +1293,10 @@
         <v>0.000291</v>
       </c>
       <c r="C50" t="n">
-        <v>0.002619999999999999</v>
+        <v>0.00258</v>
       </c>
       <c r="D50" t="n">
-        <v>0.002619999999999999</v>
+        <v>0.00258</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>31.795</v>
@@ -1310,10 +1310,10 @@
         <v>0.00029</v>
       </c>
       <c r="C51" t="n">
-        <v>0.002625</v>
+        <v>0.00257</v>
       </c>
       <c r="D51" t="n">
-        <v>0.002625</v>
+        <v>0.00257</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>31.817</v>
@@ -1327,12 +1327,12 @@
         <v>0.000288</v>
       </c>
       <c r="C52" t="n">
-        <v>0.002634999999999999</v>
+        <v>0.00257</v>
       </c>
       <c r="D52" t="n">
-        <v>0.002634999999999999</v>
-      </c>
-      <c r="E52" s="2" t="n">
+        <v>0.00257</v>
+      </c>
+      <c r="E52" t="n">
         <v>31.791</v>
       </c>
     </row>
@@ -1344,10 +1344,10 @@
         <v>0.000287</v>
       </c>
       <c r="C53" t="n">
-        <v>0.00258</v>
+        <v>0.0025</v>
       </c>
       <c r="D53" t="n">
-        <v>0.00258</v>
+        <v>0.0025</v>
       </c>
       <c r="E53" t="n">
         <v>31.736</v>
@@ -1361,12 +1361,12 @@
         <v>0.000285</v>
       </c>
       <c r="C54" t="n">
-        <v>0.00265</v>
+        <v>0.00258</v>
       </c>
       <c r="D54" t="n">
-        <v>0.00265</v>
-      </c>
-      <c r="E54" s="2" t="n">
+        <v>0.00258</v>
+      </c>
+      <c r="E54" t="n">
         <v>31.575</v>
       </c>
     </row>
@@ -1378,10 +1378,10 @@
         <v>0.000284</v>
       </c>
       <c r="C55" t="n">
-        <v>0.00256</v>
+        <v>0.002549999999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>0.00256</v>
+        <v>0.002549999999999999</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>31.857</v>
@@ -1395,12 +1395,12 @@
         <v>0.000282</v>
       </c>
       <c r="C56" t="n">
-        <v>0.002599999999999999</v>
+        <v>0.00261</v>
       </c>
       <c r="D56" t="n">
-        <v>0.002599999999999999</v>
-      </c>
-      <c r="E56" s="2" t="n">
+        <v>0.00261</v>
+      </c>
+      <c r="E56" t="n">
         <v>31.523</v>
       </c>
     </row>
@@ -1412,10 +1412,10 @@
         <v>0.00028</v>
       </c>
       <c r="C57" t="n">
-        <v>0.00266</v>
+        <v>0.00251</v>
       </c>
       <c r="D57" t="n">
-        <v>0.00266</v>
+        <v>0.00251</v>
       </c>
       <c r="E57" t="n">
         <v>31.793</v>
@@ -1429,10 +1429,10 @@
         <v>0.000279</v>
       </c>
       <c r="C58" t="n">
-        <v>0.00262</v>
+        <v>0.00254</v>
       </c>
       <c r="D58" t="n">
-        <v>0.00262</v>
+        <v>0.00254</v>
       </c>
       <c r="E58" t="n">
         <v>31.769</v>
@@ -1446,10 +1446,10 @@
         <v>0.000277</v>
       </c>
       <c r="C59" t="n">
-        <v>0.00261</v>
+        <v>0.00251</v>
       </c>
       <c r="D59" t="n">
-        <v>0.00261</v>
+        <v>0.00251</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>31.876</v>
@@ -1463,12 +1463,12 @@
         <v>0.000275</v>
       </c>
       <c r="C60" t="n">
-        <v>0.002605000000000001</v>
+        <v>0.00249</v>
       </c>
       <c r="D60" t="n">
-        <v>0.002605000000000001</v>
-      </c>
-      <c r="E60" s="2" t="n">
+        <v>0.00249</v>
+      </c>
+      <c r="E60" t="n">
         <v>31.755</v>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
         <v>0.000274</v>
       </c>
       <c r="C61" t="n">
-        <v>0.00258</v>
+        <v>0.00254</v>
       </c>
       <c r="D61" t="n">
-        <v>0.00258</v>
-      </c>
-      <c r="E61" s="2" t="n">
+        <v>0.00254</v>
+      </c>
+      <c r="E61" t="n">
         <v>31.861</v>
       </c>
     </row>
@@ -1497,10 +1497,10 @@
         <v>0.000272</v>
       </c>
       <c r="C62" t="n">
-        <v>0.002585</v>
+        <v>0.00258</v>
       </c>
       <c r="D62" t="n">
-        <v>0.002585</v>
+        <v>0.00258</v>
       </c>
       <c r="E62" t="n">
         <v>31.839</v>
@@ -1514,10 +1514,10 @@
         <v>0.00027</v>
       </c>
       <c r="C63" t="n">
-        <v>0.002595000000000001</v>
+        <v>0.00254</v>
       </c>
       <c r="D63" t="n">
-        <v>0.002595000000000001</v>
+        <v>0.00254</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>31.877</v>
@@ -1531,10 +1531,10 @@
         <v>0.000268</v>
       </c>
       <c r="C64" t="n">
-        <v>0.002565</v>
+        <v>0.00251</v>
       </c>
       <c r="D64" t="n">
-        <v>0.002565</v>
+        <v>0.00251</v>
       </c>
       <c r="E64" t="n">
         <v>31.679</v>
@@ -1548,10 +1548,10 @@
         <v>0.000267</v>
       </c>
       <c r="C65" t="n">
-        <v>0.00247</v>
+        <v>0.00234</v>
       </c>
       <c r="D65" t="n">
-        <v>0.00247</v>
+        <v>0.00234</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>31.89</v>
@@ -1565,10 +1565,10 @@
         <v>0.000265</v>
       </c>
       <c r="C66" t="n">
-        <v>0.002550000000000001</v>
+        <v>0.00252</v>
       </c>
       <c r="D66" t="n">
-        <v>0.002550000000000001</v>
+        <v>0.00252</v>
       </c>
       <c r="E66" t="n">
         <v>31.849</v>
@@ -1599,12 +1599,12 @@
         <v>0.000261</v>
       </c>
       <c r="C68" t="n">
-        <v>0.002590000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="D68" t="n">
-        <v>0.002590000000000001</v>
-      </c>
-      <c r="E68" s="2" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="E68" t="n">
         <v>31.894</v>
       </c>
     </row>
@@ -1616,10 +1616,10 @@
         <v>0.000259</v>
       </c>
       <c r="C69" t="n">
-        <v>0.00263</v>
+        <v>0.00249</v>
       </c>
       <c r="D69" t="n">
-        <v>0.00263</v>
+        <v>0.00249</v>
       </c>
       <c r="E69" t="n">
         <v>31.919</v>
@@ -1633,10 +1633,10 @@
         <v>0.000257</v>
       </c>
       <c r="C70" t="n">
-        <v>0.00258</v>
+        <v>0.00254</v>
       </c>
       <c r="D70" t="n">
-        <v>0.00258</v>
+        <v>0.00254</v>
       </c>
       <c r="E70" t="n">
         <v>31.906</v>
@@ -1650,10 +1650,10 @@
         <v>0.000255</v>
       </c>
       <c r="C71" t="n">
-        <v>0.002525000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="D71" t="n">
-        <v>0.002525000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="E71" t="n">
         <v>31.78</v>
@@ -1667,10 +1667,10 @@
         <v>0.000253</v>
       </c>
       <c r="C72" t="n">
-        <v>0.002590000000000001</v>
+        <v>0.00249</v>
       </c>
       <c r="D72" t="n">
-        <v>0.002590000000000001</v>
+        <v>0.00249</v>
       </c>
       <c r="E72" t="n">
         <v>31.934</v>
@@ -1684,10 +1684,10 @@
         <v>0.000251</v>
       </c>
       <c r="C73" t="n">
-        <v>0.002560000000000001</v>
+        <v>0.00251</v>
       </c>
       <c r="D73" t="n">
-        <v>0.002560000000000001</v>
+        <v>0.00251</v>
       </c>
       <c r="E73" t="n">
         <v>31.929</v>
@@ -1701,10 +1701,10 @@
         <v>0.000249</v>
       </c>
       <c r="C74" t="n">
-        <v>0.002565</v>
+        <v>0.00252</v>
       </c>
       <c r="D74" t="n">
-        <v>0.002565</v>
+        <v>0.00252</v>
       </c>
       <c r="E74" t="n">
         <v>31.942</v>
@@ -1718,12 +1718,12 @@
         <v>0.000247</v>
       </c>
       <c r="C75" t="n">
-        <v>0.002615000000000001</v>
+        <v>0.00254</v>
       </c>
       <c r="D75" t="n">
-        <v>0.002615000000000001</v>
-      </c>
-      <c r="E75" s="2" t="n">
+        <v>0.00254</v>
+      </c>
+      <c r="E75" t="n">
         <v>31.949</v>
       </c>
     </row>
@@ -1735,10 +1735,10 @@
         <v>0.000245</v>
       </c>
       <c r="C76" t="n">
-        <v>0.002535</v>
+        <v>0.00249</v>
       </c>
       <c r="D76" t="n">
-        <v>0.002535</v>
+        <v>0.00249</v>
       </c>
       <c r="E76" t="n">
         <v>31.751</v>
@@ -1752,10 +1752,10 @@
         <v>0.000243</v>
       </c>
       <c r="C77" t="n">
-        <v>0.00255</v>
+        <v>0.00251</v>
       </c>
       <c r="D77" t="n">
-        <v>0.00255</v>
+        <v>0.00251</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>31.989</v>
@@ -1769,10 +1769,10 @@
         <v>0.000241</v>
       </c>
       <c r="C78" t="n">
-        <v>0.00252</v>
+        <v>0.00244</v>
       </c>
       <c r="D78" t="n">
-        <v>0.00252</v>
+        <v>0.00244</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>32.007</v>
@@ -1786,10 +1786,10 @@
         <v>0.000239</v>
       </c>
       <c r="C79" t="n">
-        <v>0.002585</v>
+        <v>0.00259</v>
       </c>
       <c r="D79" t="n">
-        <v>0.002585</v>
+        <v>0.00259</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>32.011</v>
@@ -1803,10 +1803,10 @@
         <v>0.000237</v>
       </c>
       <c r="C80" t="n">
-        <v>0.002565</v>
+        <v>0.00252</v>
       </c>
       <c r="D80" t="n">
-        <v>0.002565</v>
+        <v>0.00252</v>
       </c>
       <c r="E80" t="n">
         <v>31.935</v>
@@ -1820,10 +1820,10 @@
         <v>0.000235</v>
       </c>
       <c r="C81" t="n">
-        <v>0.002560000000000001</v>
+        <v>0.00246</v>
       </c>
       <c r="D81" t="n">
-        <v>0.002560000000000001</v>
+        <v>0.00246</v>
       </c>
       <c r="E81" t="n">
         <v>32.006</v>
@@ -1837,12 +1837,12 @@
         <v>0.000233</v>
       </c>
       <c r="C82" t="n">
-        <v>0.002475</v>
+        <v>0.002429999999999999</v>
       </c>
       <c r="D82" t="n">
-        <v>0.002475</v>
-      </c>
-      <c r="E82" s="2" t="n">
+        <v>0.002429999999999999</v>
+      </c>
+      <c r="E82" t="n">
         <v>31.911</v>
       </c>
     </row>
@@ -1854,10 +1854,10 @@
         <v>0.000231</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0025</v>
+        <v>0.00249</v>
       </c>
       <c r="D83" t="n">
-        <v>0.0025</v>
+        <v>0.00249</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>32.013</v>
@@ -1871,10 +1871,10 @@
         <v>0.000228</v>
       </c>
       <c r="C84" t="n">
-        <v>0.002475</v>
+        <v>0.00244</v>
       </c>
       <c r="D84" t="n">
-        <v>0.002475</v>
+        <v>0.00244</v>
       </c>
       <c r="E84" t="n">
         <v>31.914</v>
@@ -1888,10 +1888,10 @@
         <v>0.000226</v>
       </c>
       <c r="C85" t="n">
-        <v>0.00253</v>
+        <v>0.00247</v>
       </c>
       <c r="D85" t="n">
-        <v>0.00253</v>
+        <v>0.00247</v>
       </c>
       <c r="E85" t="n">
         <v>31.908</v>
@@ -1905,10 +1905,10 @@
         <v>0.000224</v>
       </c>
       <c r="C86" t="n">
-        <v>0.002585</v>
+        <v>0.00259</v>
       </c>
       <c r="D86" t="n">
-        <v>0.002585</v>
+        <v>0.00259</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>32.021</v>
@@ -1922,10 +1922,10 @@
         <v>0.000222</v>
       </c>
       <c r="C87" t="n">
-        <v>0.002545</v>
+        <v>0.00246</v>
       </c>
       <c r="D87" t="n">
-        <v>0.002545</v>
+        <v>0.00246</v>
       </c>
       <c r="E87" t="n">
         <v>31.945</v>
@@ -1939,12 +1939,12 @@
         <v>0.00022</v>
       </c>
       <c r="C88" t="n">
-        <v>0.002525</v>
+        <v>0.00244</v>
       </c>
       <c r="D88" t="n">
-        <v>0.002525</v>
-      </c>
-      <c r="E88" s="2" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="E88" t="n">
         <v>32.003</v>
       </c>
     </row>
@@ -1956,10 +1956,10 @@
         <v>0.000218</v>
       </c>
       <c r="C89" t="n">
-        <v>0.00253</v>
+        <v>0.002449999999999999</v>
       </c>
       <c r="D89" t="n">
-        <v>0.00253</v>
+        <v>0.002449999999999999</v>
       </c>
       <c r="E89" t="n">
         <v>31.943</v>
@@ -1973,10 +1973,10 @@
         <v>0.000215</v>
       </c>
       <c r="C90" t="n">
-        <v>0.002595000000000001</v>
+        <v>0.00249</v>
       </c>
       <c r="D90" t="n">
-        <v>0.002595000000000001</v>
+        <v>0.00249</v>
       </c>
       <c r="E90" t="n">
         <v>32.008</v>
@@ -1990,10 +1990,10 @@
         <v>0.000213</v>
       </c>
       <c r="C91" t="n">
-        <v>0.002550000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="D91" t="n">
-        <v>0.002550000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="E91" t="n">
         <v>31.911</v>
@@ -2007,12 +2007,12 @@
         <v>0.000211</v>
       </c>
       <c r="C92" t="n">
-        <v>0.00258</v>
+        <v>0.00251</v>
       </c>
       <c r="D92" t="n">
-        <v>0.00258</v>
-      </c>
-      <c r="E92" s="2" t="n">
+        <v>0.00251</v>
+      </c>
+      <c r="E92" t="n">
         <v>31.982</v>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
         <v>0.000209</v>
       </c>
       <c r="C93" t="n">
-        <v>0.00251</v>
+        <v>0.002429999999999999</v>
       </c>
       <c r="D93" t="n">
-        <v>0.00251</v>
-      </c>
-      <c r="E93" s="2" t="n">
+        <v>0.002429999999999999</v>
+      </c>
+      <c r="E93" t="n">
         <v>31.944</v>
       </c>
     </row>
@@ -2041,12 +2041,12 @@
         <v>0.000206</v>
       </c>
       <c r="C94" t="n">
-        <v>0.00253</v>
+        <v>0.00248</v>
       </c>
       <c r="D94" t="n">
-        <v>0.00253</v>
-      </c>
-      <c r="E94" s="2" t="n">
+        <v>0.00248</v>
+      </c>
+      <c r="E94" t="n">
         <v>31.987</v>
       </c>
     </row>
@@ -2058,12 +2058,12 @@
         <v>0.000204</v>
       </c>
       <c r="C95" t="n">
-        <v>0.00249</v>
+        <v>0.00242</v>
       </c>
       <c r="D95" t="n">
-        <v>0.00249</v>
-      </c>
-      <c r="E95" s="2" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="E95" t="n">
         <v>31.998</v>
       </c>
     </row>
@@ -2075,10 +2075,10 @@
         <v>0.000202</v>
       </c>
       <c r="C96" t="n">
-        <v>0.002520000000000001</v>
+        <v>0.00246</v>
       </c>
       <c r="D96" t="n">
-        <v>0.002520000000000001</v>
+        <v>0.00246</v>
       </c>
       <c r="E96" t="n">
         <v>31.986</v>
@@ -2092,10 +2092,10 @@
         <v>0.0002</v>
       </c>
       <c r="C97" t="n">
-        <v>0.002495</v>
+        <v>0.002439999999999999</v>
       </c>
       <c r="D97" t="n">
-        <v>0.002495</v>
+        <v>0.002439999999999999</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>32.027</v>
@@ -2109,10 +2109,10 @@
         <v>0.000197</v>
       </c>
       <c r="C98" t="n">
-        <v>0.002475</v>
+        <v>0.00244</v>
       </c>
       <c r="D98" t="n">
-        <v>0.002475</v>
+        <v>0.00244</v>
       </c>
       <c r="E98" t="n">
         <v>31.985</v>
@@ -2126,10 +2126,10 @@
         <v>0.000195</v>
       </c>
       <c r="C99" t="n">
-        <v>0.002525000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="D99" t="n">
-        <v>0.002525000000000001</v>
+        <v>0.0025</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>32.06</v>
@@ -2143,10 +2143,10 @@
         <v>0.000193</v>
       </c>
       <c r="C100" t="n">
-        <v>0.00255</v>
+        <v>0.0025</v>
       </c>
       <c r="D100" t="n">
-        <v>0.00255</v>
+        <v>0.0025</v>
       </c>
       <c r="E100" t="n">
         <v>32.044</v>
@@ -2160,10 +2160,10 @@
         <v>0.00019</v>
       </c>
       <c r="C101" t="n">
-        <v>0.002475</v>
+        <v>0.0024</v>
       </c>
       <c r="D101" t="n">
-        <v>0.002475</v>
+        <v>0.0024</v>
       </c>
       <c r="E101" t="n">
         <v>32.06</v>
@@ -2177,10 +2177,10 @@
         <v>0.000188</v>
       </c>
       <c r="C102" t="n">
-        <v>0.002475</v>
+        <v>0.00236</v>
       </c>
       <c r="D102" t="n">
-        <v>0.002475</v>
+        <v>0.00236</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>32.061</v>
@@ -2194,10 +2194,10 @@
         <v>0.000186</v>
       </c>
       <c r="C103" t="n">
-        <v>0.00248</v>
+        <v>0.00239</v>
       </c>
       <c r="D103" t="n">
-        <v>0.00248</v>
+        <v>0.00239</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>32.068</v>
@@ -2211,12 +2211,12 @@
         <v>0.000183</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0025</v>
+        <v>0.0024</v>
       </c>
       <c r="D104" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="E104" s="2" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E104" t="n">
         <v>32.042</v>
       </c>
     </row>
@@ -2228,10 +2228,10 @@
         <v>0.000181</v>
       </c>
       <c r="C105" t="n">
-        <v>0.002525</v>
+        <v>0.00249</v>
       </c>
       <c r="D105" t="n">
-        <v>0.002525</v>
+        <v>0.00249</v>
       </c>
       <c r="E105" t="n">
         <v>32.022</v>
@@ -2245,10 +2245,10 @@
         <v>0.000179</v>
       </c>
       <c r="C106" t="n">
-        <v>0.002510000000000001</v>
+        <v>0.00245</v>
       </c>
       <c r="D106" t="n">
-        <v>0.002510000000000001</v>
+        <v>0.00245</v>
       </c>
       <c r="E106" t="n">
         <v>32.067</v>
@@ -2262,10 +2262,10 @@
         <v>0.000176</v>
       </c>
       <c r="C107" t="n">
-        <v>0.00248</v>
+        <v>0.0024</v>
       </c>
       <c r="D107" t="n">
-        <v>0.00248</v>
+        <v>0.0024</v>
       </c>
       <c r="E107" t="n">
         <v>32.045</v>
@@ -2279,12 +2279,12 @@
         <v>0.000174</v>
       </c>
       <c r="C108" t="n">
-        <v>0.002495</v>
+        <v>0.0024</v>
       </c>
       <c r="D108" t="n">
-        <v>0.002495</v>
-      </c>
-      <c r="E108" s="2" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E108" t="n">
         <v>31.991</v>
       </c>
     </row>
@@ -2296,10 +2296,10 @@
         <v>0.000172</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0025</v>
+        <v>0.00239</v>
       </c>
       <c r="D109" t="n">
-        <v>0.0025</v>
+        <v>0.00239</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>32.123</v>
@@ -2313,10 +2313,10 @@
         <v>0.000169</v>
       </c>
       <c r="C110" t="n">
-        <v>0.00258</v>
+        <v>0.0025</v>
       </c>
       <c r="D110" t="n">
-        <v>0.00258</v>
+        <v>0.0025</v>
       </c>
       <c r="E110" t="n">
         <v>32.115</v>
@@ -2330,10 +2330,10 @@
         <v>0.000167</v>
       </c>
       <c r="C111" t="n">
-        <v>0.002530000000000001</v>
+        <v>0.00251</v>
       </c>
       <c r="D111" t="n">
-        <v>0.002530000000000001</v>
+        <v>0.00251</v>
       </c>
       <c r="E111" t="n">
         <v>32.094</v>
@@ -2347,10 +2347,10 @@
         <v>0.000165</v>
       </c>
       <c r="C112" t="n">
-        <v>0.002510000000000001</v>
+        <v>0.00244</v>
       </c>
       <c r="D112" t="n">
-        <v>0.002510000000000001</v>
+        <v>0.00244</v>
       </c>
       <c r="E112" t="n">
         <v>32.065</v>
@@ -2364,12 +2364,12 @@
         <v>0.000162</v>
       </c>
       <c r="C113" t="n">
-        <v>0.00249</v>
+        <v>0.00241</v>
       </c>
       <c r="D113" t="n">
-        <v>0.00249</v>
-      </c>
-      <c r="E113" s="2" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E113" t="n">
         <v>32.118</v>
       </c>
     </row>
@@ -2381,10 +2381,10 @@
         <v>0.00016</v>
       </c>
       <c r="C114" t="n">
-        <v>0.002429999999999999</v>
+        <v>0.00239</v>
       </c>
       <c r="D114" t="n">
-        <v>0.002429999999999999</v>
+        <v>0.00239</v>
       </c>
       <c r="E114" t="n">
         <v>32.076</v>
@@ -2398,10 +2398,10 @@
         <v>0.000158</v>
       </c>
       <c r="C115" t="n">
-        <v>0.002495</v>
+        <v>0.00248</v>
       </c>
       <c r="D115" t="n">
-        <v>0.002495</v>
+        <v>0.00248</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>32.153</v>
@@ -2415,10 +2415,10 @@
         <v>0.000155</v>
       </c>
       <c r="C116" t="n">
-        <v>0.00244</v>
+        <v>0.00237</v>
       </c>
       <c r="D116" t="n">
-        <v>0.00244</v>
+        <v>0.00237</v>
       </c>
       <c r="E116" t="n">
         <v>32.116</v>
@@ -2432,12 +2432,12 @@
         <v>0.000153</v>
       </c>
       <c r="C117" t="n">
-        <v>0.002495</v>
+        <v>0.00244</v>
       </c>
       <c r="D117" t="n">
-        <v>0.002495</v>
-      </c>
-      <c r="E117" s="2" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="E117" t="n">
         <v>32.093</v>
       </c>
     </row>
@@ -2449,10 +2449,10 @@
         <v>0.000151</v>
       </c>
       <c r="C118" t="n">
-        <v>0.002504999999999999</v>
+        <v>0.00242</v>
       </c>
       <c r="D118" t="n">
-        <v>0.002504999999999999</v>
+        <v>0.00242</v>
       </c>
       <c r="E118" t="n">
         <v>32.12</v>
@@ -2466,10 +2466,10 @@
         <v>0.000148</v>
       </c>
       <c r="C119" t="n">
-        <v>0.00245</v>
+        <v>0.00235</v>
       </c>
       <c r="D119" t="n">
-        <v>0.00245</v>
+        <v>0.00235</v>
       </c>
       <c r="E119" t="n">
         <v>32.138</v>
@@ -2483,10 +2483,10 @@
         <v>0.000146</v>
       </c>
       <c r="C120" t="n">
-        <v>0.00248</v>
+        <v>0.002379999999999999</v>
       </c>
       <c r="D120" t="n">
-        <v>0.00248</v>
+        <v>0.002379999999999999</v>
       </c>
       <c r="E120" t="n">
         <v>32.095</v>
@@ -2500,10 +2500,10 @@
         <v>0.000144</v>
       </c>
       <c r="C121" t="n">
-        <v>0.002445</v>
+        <v>0.00239</v>
       </c>
       <c r="D121" t="n">
-        <v>0.002445</v>
+        <v>0.00239</v>
       </c>
       <c r="E121" t="n">
         <v>32.083</v>
@@ -2517,10 +2517,10 @@
         <v>0.000141</v>
       </c>
       <c r="C122" t="n">
-        <v>0.002520000000000001</v>
+        <v>0.00248</v>
       </c>
       <c r="D122" t="n">
-        <v>0.002520000000000001</v>
+        <v>0.00248</v>
       </c>
       <c r="E122" t="n">
         <v>32.112</v>
@@ -2534,10 +2534,10 @@
         <v>0.000139</v>
       </c>
       <c r="C123" t="n">
-        <v>0.00244</v>
+        <v>0.0024</v>
       </c>
       <c r="D123" t="n">
-        <v>0.00244</v>
+        <v>0.0024</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>32.17</v>
@@ -2551,12 +2551,12 @@
         <v>0.000137</v>
       </c>
       <c r="C124" t="n">
-        <v>0.00247</v>
+        <v>0.00236</v>
       </c>
       <c r="D124" t="n">
-        <v>0.00247</v>
-      </c>
-      <c r="E124" s="2" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E124" t="n">
         <v>32.123</v>
       </c>
     </row>
@@ -2568,10 +2568,10 @@
         <v>0.000134</v>
       </c>
       <c r="C125" t="n">
-        <v>0.002465</v>
+        <v>0.00236</v>
       </c>
       <c r="D125" t="n">
-        <v>0.002465</v>
+        <v>0.00236</v>
       </c>
       <c r="E125" t="n">
         <v>32.122</v>
@@ -2585,10 +2585,10 @@
         <v>0.000132</v>
       </c>
       <c r="C126" t="n">
-        <v>0.00249</v>
+        <v>0.00246</v>
       </c>
       <c r="D126" t="n">
-        <v>0.00249</v>
+        <v>0.00246</v>
       </c>
       <c r="E126" t="n">
         <v>32.146</v>
@@ -2602,10 +2602,10 @@
         <v>0.00013</v>
       </c>
       <c r="C127" t="n">
-        <v>0.002505</v>
+        <v>0.0025</v>
       </c>
       <c r="D127" t="n">
-        <v>0.002505</v>
+        <v>0.0025</v>
       </c>
       <c r="E127" t="n">
         <v>32.146</v>
@@ -2619,10 +2619,10 @@
         <v>0.000128</v>
       </c>
       <c r="C128" t="n">
-        <v>0.00248</v>
+        <v>0.00243</v>
       </c>
       <c r="D128" t="n">
-        <v>0.00248</v>
+        <v>0.00243</v>
       </c>
       <c r="E128" t="n">
         <v>32.13</v>
@@ -2636,10 +2636,10 @@
         <v>0.000125</v>
       </c>
       <c r="C129" t="n">
-        <v>0.00248</v>
+        <v>0.00247</v>
       </c>
       <c r="D129" t="n">
-        <v>0.00248</v>
+        <v>0.00247</v>
       </c>
       <c r="E129" t="n">
         <v>32.143</v>
@@ -2653,10 +2653,10 @@
         <v>0.000123</v>
       </c>
       <c r="C130" t="n">
-        <v>0.002550000000000001</v>
+        <v>0.00251</v>
       </c>
       <c r="D130" t="n">
-        <v>0.002550000000000001</v>
+        <v>0.00251</v>
       </c>
       <c r="E130" t="n">
         <v>32.119</v>
@@ -2670,12 +2670,12 @@
         <v>0.000121</v>
       </c>
       <c r="C131" t="n">
-        <v>0.002495</v>
+        <v>0.00241</v>
       </c>
       <c r="D131" t="n">
-        <v>0.002495</v>
-      </c>
-      <c r="E131" s="2" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E131" t="n">
         <v>32.15</v>
       </c>
     </row>
@@ -2687,12 +2687,12 @@
         <v>0.000119</v>
       </c>
       <c r="C132" t="n">
-        <v>0.002495</v>
+        <v>0.002429999999999999</v>
       </c>
       <c r="D132" t="n">
-        <v>0.002495</v>
-      </c>
-      <c r="E132" s="2" t="n">
+        <v>0.002429999999999999</v>
+      </c>
+      <c r="E132" t="n">
         <v>32.119</v>
       </c>
     </row>
@@ -2704,10 +2704,10 @@
         <v>0.000116</v>
       </c>
       <c r="C133" t="n">
-        <v>0.002445</v>
+        <v>0.00236</v>
       </c>
       <c r="D133" t="n">
-        <v>0.002445</v>
+        <v>0.00236</v>
       </c>
       <c r="E133" t="n">
         <v>32.124</v>
@@ -2721,10 +2721,10 @@
         <v>0.000114</v>
       </c>
       <c r="C134" t="n">
-        <v>0.002515</v>
+        <v>0.00245</v>
       </c>
       <c r="D134" t="n">
-        <v>0.002515</v>
+        <v>0.00245</v>
       </c>
       <c r="E134" t="n">
         <v>32.141</v>
@@ -2738,10 +2738,10 @@
         <v>0.000112</v>
       </c>
       <c r="C135" t="n">
-        <v>0.002525</v>
+        <v>0.00247</v>
       </c>
       <c r="D135" t="n">
-        <v>0.002525</v>
+        <v>0.00247</v>
       </c>
       <c r="E135" t="n">
         <v>32.163</v>
@@ -2755,10 +2755,10 @@
         <v>0.00011</v>
       </c>
       <c r="C136" t="n">
-        <v>0.0025</v>
+        <v>0.00247</v>
       </c>
       <c r="D136" t="n">
-        <v>0.0025</v>
+        <v>0.00247</v>
       </c>
       <c r="E136" t="n">
         <v>32.107</v>
@@ -2789,10 +2789,10 @@
         <v>0.000105</v>
       </c>
       <c r="C138" t="n">
-        <v>0.00247</v>
+        <v>0.0024</v>
       </c>
       <c r="D138" t="n">
-        <v>0.00247</v>
+        <v>0.0024</v>
       </c>
       <c r="E138" t="n">
         <v>32.164</v>
@@ -2806,10 +2806,10 @@
         <v>0.000103</v>
       </c>
       <c r="C139" t="n">
-        <v>0.002465</v>
+        <v>0.00245</v>
       </c>
       <c r="D139" t="n">
-        <v>0.002465</v>
+        <v>0.00245</v>
       </c>
       <c r="E139" t="n">
         <v>32.168</v>
@@ -2823,10 +2823,10 @@
         <v>0.000101</v>
       </c>
       <c r="C140" t="n">
-        <v>0.002415</v>
+        <v>0.00234</v>
       </c>
       <c r="D140" t="n">
-        <v>0.002415</v>
+        <v>0.00234</v>
       </c>
       <c r="E140" t="n">
         <v>32.156</v>
@@ -2840,10 +2840,10 @@
         <v>9.88e-05</v>
       </c>
       <c r="C141" t="n">
-        <v>0.002455</v>
+        <v>0.002379999999999999</v>
       </c>
       <c r="D141" t="n">
-        <v>0.002455</v>
+        <v>0.002379999999999999</v>
       </c>
       <c r="E141" t="n">
         <v>32.155</v>
@@ -2857,10 +2857,10 @@
         <v>9.670000000000001e-05</v>
       </c>
       <c r="C142" t="n">
-        <v>0.002475000000000001</v>
+        <v>0.00243</v>
       </c>
       <c r="D142" t="n">
-        <v>0.002475000000000001</v>
+        <v>0.00243</v>
       </c>
       <c r="E142" s="2" t="n">
         <v>32.179</v>
@@ -2874,10 +2874,10 @@
         <v>9.46e-05</v>
       </c>
       <c r="C143" t="n">
-        <v>0.002455</v>
+        <v>0.00239</v>
       </c>
       <c r="D143" t="n">
-        <v>0.002455</v>
+        <v>0.00239</v>
       </c>
       <c r="E143" s="2" t="n">
         <v>32.188</v>
@@ -2891,10 +2891,10 @@
         <v>9.25e-05</v>
       </c>
       <c r="C144" t="n">
-        <v>0.002455</v>
+        <v>0.002429999999999999</v>
       </c>
       <c r="D144" t="n">
-        <v>0.002455</v>
+        <v>0.002429999999999999</v>
       </c>
       <c r="E144" t="n">
         <v>32.165</v>
@@ -2908,12 +2908,12 @@
         <v>9.04e-05</v>
       </c>
       <c r="C145" t="n">
-        <v>0.00249</v>
+        <v>0.00239</v>
       </c>
       <c r="D145" t="n">
-        <v>0.00249</v>
-      </c>
-      <c r="E145" s="2" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E145" t="n">
         <v>32.183</v>
       </c>
     </row>
@@ -2925,12 +2925,12 @@
         <v>8.830000000000001e-05</v>
       </c>
       <c r="C146" t="n">
-        <v>0.002475</v>
+        <v>0.00243</v>
       </c>
       <c r="D146" t="n">
-        <v>0.002475</v>
-      </c>
-      <c r="E146" s="2" t="n">
+        <v>0.00243</v>
+      </c>
+      <c r="E146" t="n">
         <v>32.175</v>
       </c>
     </row>
@@ -2942,10 +2942,10 @@
         <v>8.63e-05</v>
       </c>
       <c r="C147" t="n">
-        <v>0.00245</v>
+        <v>0.00239</v>
       </c>
       <c r="D147" t="n">
-        <v>0.00245</v>
+        <v>0.00239</v>
       </c>
       <c r="E147" t="n">
         <v>32.178</v>
@@ -2959,10 +2959,10 @@
         <v>8.42e-05</v>
       </c>
       <c r="C148" t="n">
-        <v>0.00245</v>
+        <v>0.00239</v>
       </c>
       <c r="D148" t="n">
-        <v>0.00245</v>
+        <v>0.00239</v>
       </c>
       <c r="E148" t="n">
         <v>32.176</v>
@@ -2976,10 +2976,10 @@
         <v>8.220000000000001e-05</v>
       </c>
       <c r="C149" t="n">
-        <v>0.00251</v>
+        <v>0.002429999999999999</v>
       </c>
       <c r="D149" t="n">
-        <v>0.00251</v>
+        <v>0.002429999999999999</v>
       </c>
       <c r="E149" t="n">
         <v>32.177</v>
@@ -2993,10 +2993,10 @@
         <v>8.02e-05</v>
       </c>
       <c r="C150" t="n">
-        <v>0.002495</v>
+        <v>0.00245</v>
       </c>
       <c r="D150" t="n">
-        <v>0.002495</v>
+        <v>0.00245</v>
       </c>
       <c r="E150" t="n">
         <v>32.167</v>
@@ -3010,10 +3010,10 @@
         <v>7.82e-05</v>
       </c>
       <c r="C151" t="n">
-        <v>0.00243</v>
+        <v>0.00237</v>
       </c>
       <c r="D151" t="n">
-        <v>0.00243</v>
+        <v>0.00237</v>
       </c>
       <c r="E151" t="n">
         <v>32.173</v>
@@ -3027,10 +3027,10 @@
         <v>7.62e-05</v>
       </c>
       <c r="C152" t="n">
-        <v>0.002399999999999999</v>
+        <v>0.00233</v>
       </c>
       <c r="D152" t="n">
-        <v>0.002399999999999999</v>
+        <v>0.00233</v>
       </c>
       <c r="E152" s="2" t="n">
         <v>32.2</v>
@@ -3044,12 +3044,12 @@
         <v>7.42e-05</v>
       </c>
       <c r="C153" t="n">
-        <v>0.00245</v>
+        <v>0.00242</v>
       </c>
       <c r="D153" t="n">
-        <v>0.00245</v>
-      </c>
-      <c r="E153" s="2" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="E153" t="n">
         <v>32.196</v>
       </c>
     </row>
@@ -3061,10 +3061,10 @@
         <v>7.23e-05</v>
       </c>
       <c r="C154" t="n">
-        <v>0.00246</v>
+        <v>0.00235</v>
       </c>
       <c r="D154" t="n">
-        <v>0.00246</v>
+        <v>0.00235</v>
       </c>
       <c r="E154" t="n">
         <v>32.184</v>
@@ -3078,10 +3078,10 @@
         <v>7.04e-05</v>
       </c>
       <c r="C155" t="n">
-        <v>0.002465</v>
+        <v>0.00242</v>
       </c>
       <c r="D155" t="n">
-        <v>0.002465</v>
+        <v>0.00242</v>
       </c>
       <c r="E155" t="n">
         <v>32.196</v>
@@ -3095,10 +3095,10 @@
         <v>6.85e-05</v>
       </c>
       <c r="C156" t="n">
-        <v>0.002485</v>
+        <v>0.00244</v>
       </c>
       <c r="D156" t="n">
-        <v>0.002485</v>
+        <v>0.00244</v>
       </c>
       <c r="E156" t="n">
         <v>32.19</v>
@@ -3112,12 +3112,12 @@
         <v>6.660000000000001e-05</v>
       </c>
       <c r="C157" t="n">
-        <v>0.002405</v>
+        <v>0.0024</v>
       </c>
       <c r="D157" t="n">
-        <v>0.002405</v>
-      </c>
-      <c r="E157" s="2" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E157" t="n">
         <v>32.183</v>
       </c>
     </row>
@@ -3129,10 +3129,10 @@
         <v>6.47e-05</v>
       </c>
       <c r="C158" t="n">
-        <v>0.00247</v>
+        <v>0.00241</v>
       </c>
       <c r="D158" t="n">
-        <v>0.00247</v>
+        <v>0.00241</v>
       </c>
       <c r="E158" t="n">
         <v>32.189</v>
@@ -3146,10 +3146,10 @@
         <v>6.29e-05</v>
       </c>
       <c r="C159" t="n">
-        <v>0.00245</v>
+        <v>0.00239</v>
       </c>
       <c r="D159" t="n">
-        <v>0.00245</v>
+        <v>0.00239</v>
       </c>
       <c r="E159" t="n">
         <v>32.182</v>
@@ -3163,10 +3163,10 @@
         <v>6.109999999999999e-05</v>
       </c>
       <c r="C160" t="n">
-        <v>0.00245</v>
+        <v>0.00239</v>
       </c>
       <c r="D160" t="n">
-        <v>0.00245</v>
+        <v>0.00239</v>
       </c>
       <c r="E160" t="n">
         <v>32.165</v>
@@ -3180,10 +3180,10 @@
         <v>5.93e-05</v>
       </c>
       <c r="C161" t="n">
-        <v>0.002445</v>
+        <v>0.00239</v>
       </c>
       <c r="D161" t="n">
-        <v>0.002445</v>
+        <v>0.00239</v>
       </c>
       <c r="E161" s="2" t="n">
         <v>32.203</v>
@@ -3197,10 +3197,10 @@
         <v>5.75e-05</v>
       </c>
       <c r="C162" t="n">
-        <v>0.00239</v>
+        <v>0.00236</v>
       </c>
       <c r="D162" t="n">
-        <v>0.00239</v>
+        <v>0.00236</v>
       </c>
       <c r="E162" s="2" t="n">
         <v>32.203</v>
@@ -3214,10 +3214,10 @@
         <v>5.57e-05</v>
       </c>
       <c r="C163" t="n">
-        <v>0.00248</v>
+        <v>0.00244</v>
       </c>
       <c r="D163" t="n">
-        <v>0.00248</v>
+        <v>0.00244</v>
       </c>
       <c r="E163" s="2" t="n">
         <v>32.226</v>
@@ -3231,10 +3231,10 @@
         <v>5.4e-05</v>
       </c>
       <c r="C164" t="n">
-        <v>0.002515000000000001</v>
+        <v>0.00251</v>
       </c>
       <c r="D164" t="n">
-        <v>0.002515000000000001</v>
+        <v>0.00251</v>
       </c>
       <c r="E164" t="n">
         <v>32.201</v>
@@ -3248,10 +3248,10 @@
         <v>5.23e-05</v>
       </c>
       <c r="C165" t="n">
-        <v>0.00245</v>
+        <v>0.00241</v>
       </c>
       <c r="D165" t="n">
-        <v>0.00245</v>
+        <v>0.00241</v>
       </c>
       <c r="E165" t="n">
         <v>32.208</v>
@@ -3265,10 +3265,10 @@
         <v>5.06e-05</v>
       </c>
       <c r="C166" t="n">
-        <v>0.002369999999999999</v>
+        <v>0.00229</v>
       </c>
       <c r="D166" t="n">
-        <v>0.002369999999999999</v>
+        <v>0.00229</v>
       </c>
       <c r="E166" t="n">
         <v>32.195</v>
@@ -3282,12 +3282,12 @@
         <v>4.89e-05</v>
       </c>
       <c r="C167" t="n">
-        <v>0.002425</v>
+        <v>0.00235</v>
       </c>
       <c r="D167" t="n">
-        <v>0.002425</v>
-      </c>
-      <c r="E167" s="2" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="E167" t="n">
         <v>32.22</v>
       </c>
     </row>
@@ -3299,12 +3299,12 @@
         <v>4.73e-05</v>
       </c>
       <c r="C168" t="n">
-        <v>0.00242</v>
+        <v>0.00237</v>
       </c>
       <c r="D168" t="n">
-        <v>0.00242</v>
-      </c>
-      <c r="E168" s="2" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E168" t="n">
         <v>32.222</v>
       </c>
     </row>
@@ -3316,12 +3316,12 @@
         <v>4.57e-05</v>
       </c>
       <c r="C169" t="n">
-        <v>0.002445</v>
+        <v>0.00233</v>
       </c>
       <c r="D169" t="n">
-        <v>0.002445</v>
-      </c>
-      <c r="E169" s="2" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="E169" t="n">
         <v>32.194</v>
       </c>
     </row>
@@ -3333,10 +3333,10 @@
         <v>4.41e-05</v>
       </c>
       <c r="C170" t="n">
-        <v>0.002465</v>
+        <v>0.0024</v>
       </c>
       <c r="D170" t="n">
-        <v>0.002465</v>
+        <v>0.0024</v>
       </c>
       <c r="E170" t="n">
         <v>32.218</v>
@@ -3350,10 +3350,10 @@
         <v>4.25e-05</v>
       </c>
       <c r="C171" t="n">
-        <v>0.00244</v>
+        <v>0.00241</v>
       </c>
       <c r="D171" t="n">
-        <v>0.00244</v>
+        <v>0.00241</v>
       </c>
       <c r="E171" t="n">
         <v>32.213</v>
@@ -3367,10 +3367,10 @@
         <v>4.1e-05</v>
       </c>
       <c r="C172" t="n">
-        <v>0.00247</v>
+        <v>0.00243</v>
       </c>
       <c r="D172" t="n">
-        <v>0.00247</v>
+        <v>0.00243</v>
       </c>
       <c r="E172" t="n">
         <v>32.216</v>
@@ -3384,10 +3384,10 @@
         <v>3.95e-05</v>
       </c>
       <c r="C173" t="n">
-        <v>0.002435</v>
+        <v>0.00238</v>
       </c>
       <c r="D173" t="n">
-        <v>0.002435</v>
+        <v>0.00238</v>
       </c>
       <c r="E173" t="n">
         <v>32.206</v>
@@ -3401,10 +3401,10 @@
         <v>3.8e-05</v>
       </c>
       <c r="C174" t="n">
-        <v>0.00246</v>
+        <v>0.00239</v>
       </c>
       <c r="D174" t="n">
-        <v>0.00246</v>
+        <v>0.00239</v>
       </c>
       <c r="E174" t="n">
         <v>32.205</v>
@@ -3418,10 +3418,10 @@
         <v>3.65e-05</v>
       </c>
       <c r="C175" t="n">
-        <v>0.00245</v>
+        <v>0.0024</v>
       </c>
       <c r="D175" t="n">
-        <v>0.00245</v>
+        <v>0.0024</v>
       </c>
       <c r="E175" t="n">
         <v>32.213</v>
@@ -3435,12 +3435,12 @@
         <v>3.51e-05</v>
       </c>
       <c r="C176" t="n">
-        <v>0.002435</v>
+        <v>0.002379999999999999</v>
       </c>
       <c r="D176" t="n">
-        <v>0.002435</v>
-      </c>
-      <c r="E176" s="2" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="E176" t="n">
         <v>32.216</v>
       </c>
     </row>
@@ -3452,10 +3452,10 @@
         <v>3.37e-05</v>
       </c>
       <c r="C177" t="n">
-        <v>0.002459999999999999</v>
+        <v>0.00234</v>
       </c>
       <c r="D177" t="n">
-        <v>0.002459999999999999</v>
+        <v>0.00234</v>
       </c>
       <c r="E177" t="n">
         <v>32.214</v>
@@ -3469,10 +3469,10 @@
         <v>3.23e-05</v>
       </c>
       <c r="C178" t="n">
-        <v>0.0024</v>
+        <v>0.002379999999999999</v>
       </c>
       <c r="D178" t="n">
-        <v>0.0024</v>
+        <v>0.002379999999999999</v>
       </c>
       <c r="E178" t="n">
         <v>32.22</v>
@@ -3486,10 +3486,10 @@
         <v>3.09e-05</v>
       </c>
       <c r="C179" t="n">
-        <v>0.00245</v>
+        <v>0.00237</v>
       </c>
       <c r="D179" t="n">
-        <v>0.00245</v>
+        <v>0.00237</v>
       </c>
       <c r="E179" t="n">
         <v>32.217</v>
@@ -3503,12 +3503,12 @@
         <v>2.96e-05</v>
       </c>
       <c r="C180" t="n">
-        <v>0.00245</v>
+        <v>0.00239</v>
       </c>
       <c r="D180" t="n">
-        <v>0.00245</v>
-      </c>
-      <c r="E180" s="2" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E180" t="n">
         <v>32.224</v>
       </c>
     </row>
@@ -3537,10 +3537,10 @@
         <v>2.7e-05</v>
       </c>
       <c r="C182" t="n">
-        <v>0.002505</v>
+        <v>0.00249</v>
       </c>
       <c r="D182" t="n">
-        <v>0.002505</v>
+        <v>0.00249</v>
       </c>
       <c r="E182" t="n">
         <v>32.231</v>
@@ -3554,10 +3554,10 @@
         <v>2.57e-05</v>
       </c>
       <c r="C183" t="n">
-        <v>0.002429999999999999</v>
+        <v>0.00236</v>
       </c>
       <c r="D183" t="n">
-        <v>0.002429999999999999</v>
+        <v>0.00236</v>
       </c>
       <c r="E183" t="n">
         <v>32.23</v>
@@ -3571,10 +3571,10 @@
         <v>2.45e-05</v>
       </c>
       <c r="C184" t="n">
-        <v>0.002444999999999999</v>
+        <v>0.0023</v>
       </c>
       <c r="D184" t="n">
-        <v>0.002444999999999999</v>
+        <v>0.0023</v>
       </c>
       <c r="E184" s="2" t="n">
         <v>32.233</v>
@@ -3588,12 +3588,12 @@
         <v>2.33e-05</v>
       </c>
       <c r="C185" t="n">
-        <v>0.002415</v>
+        <v>0.0024</v>
       </c>
       <c r="D185" t="n">
-        <v>0.002415</v>
-      </c>
-      <c r="E185" s="2" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E185" t="n">
         <v>32.222</v>
       </c>
     </row>
@@ -3605,10 +3605,10 @@
         <v>2.22e-05</v>
       </c>
       <c r="C186" t="n">
-        <v>0.002415</v>
+        <v>0.00235</v>
       </c>
       <c r="D186" t="n">
-        <v>0.002415</v>
+        <v>0.00235</v>
       </c>
       <c r="E186" t="n">
         <v>32.231</v>
@@ -3622,10 +3622,10 @@
         <v>2.1e-05</v>
       </c>
       <c r="C187" t="n">
-        <v>0.002485</v>
+        <v>0.0024</v>
       </c>
       <c r="D187" t="n">
-        <v>0.002485</v>
+        <v>0.0024</v>
       </c>
       <c r="E187" t="n">
         <v>32.219</v>
@@ -3639,10 +3639,10 @@
         <v>1.99e-05</v>
       </c>
       <c r="C188" t="n">
-        <v>0.00241</v>
+        <v>0.00236</v>
       </c>
       <c r="D188" t="n">
-        <v>0.00241</v>
+        <v>0.00236</v>
       </c>
       <c r="E188" t="n">
         <v>32.217</v>
@@ -3656,10 +3656,10 @@
         <v>1.88e-05</v>
       </c>
       <c r="C189" t="n">
-        <v>0.00244</v>
+        <v>0.00236</v>
       </c>
       <c r="D189" t="n">
-        <v>0.00244</v>
+        <v>0.00236</v>
       </c>
       <c r="E189" s="2" t="n">
         <v>32.235</v>
@@ -3673,10 +3673,10 @@
         <v>1.78e-05</v>
       </c>
       <c r="C190" t="n">
-        <v>0.00247</v>
+        <v>0.00244</v>
       </c>
       <c r="D190" t="n">
-        <v>0.00247</v>
+        <v>0.00244</v>
       </c>
       <c r="E190" s="2" t="n">
         <v>32.237</v>
@@ -3690,10 +3690,10 @@
         <v>1.68e-05</v>
       </c>
       <c r="C191" t="n">
-        <v>0.00244</v>
+        <v>0.0024</v>
       </c>
       <c r="D191" t="n">
-        <v>0.00244</v>
+        <v>0.0024</v>
       </c>
       <c r="E191" t="n">
         <v>32.236</v>
@@ -3707,12 +3707,12 @@
         <v>1.58e-05</v>
       </c>
       <c r="C192" t="n">
-        <v>0.002455</v>
+        <v>0.0024</v>
       </c>
       <c r="D192" t="n">
-        <v>0.002455</v>
-      </c>
-      <c r="E192" s="2" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E192" t="n">
         <v>32.226</v>
       </c>
     </row>
@@ -3724,12 +3724,12 @@
         <v>1.48e-05</v>
       </c>
       <c r="C193" t="n">
-        <v>0.002425</v>
+        <v>0.002379999999999999</v>
       </c>
       <c r="D193" t="n">
-        <v>0.002425</v>
-      </c>
-      <c r="E193" s="2" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="E193" t="n">
         <v>32.227</v>
       </c>
     </row>
@@ -3741,10 +3741,10 @@
         <v>1.39e-05</v>
       </c>
       <c r="C194" t="n">
-        <v>0.00242</v>
+        <v>0.00237</v>
       </c>
       <c r="D194" t="n">
-        <v>0.00242</v>
+        <v>0.00237</v>
       </c>
       <c r="E194" t="n">
         <v>32.228</v>
@@ -3758,10 +3758,10 @@
         <v>1.3e-05</v>
       </c>
       <c r="C195" t="n">
-        <v>0.00244</v>
+        <v>0.00237</v>
       </c>
       <c r="D195" t="n">
-        <v>0.00244</v>
+        <v>0.00237</v>
       </c>
       <c r="E195" t="n">
         <v>32.235</v>
@@ -3775,12 +3775,12 @@
         <v>1.22e-05</v>
       </c>
       <c r="C196" t="n">
-        <v>0.002449999999999999</v>
+        <v>0.00238</v>
       </c>
       <c r="D196" t="n">
-        <v>0.002449999999999999</v>
-      </c>
-      <c r="E196" s="2" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="E196" t="n">
         <v>32.229</v>
       </c>
     </row>
@@ -3792,10 +3792,10 @@
         <v>1.13e-05</v>
       </c>
       <c r="C197" t="n">
-        <v>0.002485</v>
+        <v>0.00247</v>
       </c>
       <c r="D197" t="n">
-        <v>0.002485</v>
+        <v>0.00247</v>
       </c>
       <c r="E197" t="n">
         <v>32.23</v>
@@ -3809,10 +3809,10 @@
         <v>1.05e-05</v>
       </c>
       <c r="C198" t="n">
-        <v>0.002405</v>
+        <v>0.00229</v>
       </c>
       <c r="D198" t="n">
-        <v>0.002405</v>
+        <v>0.00229</v>
       </c>
       <c r="E198" s="2" t="n">
         <v>32.242</v>
@@ -3826,10 +3826,10 @@
         <v>9.75e-06</v>
       </c>
       <c r="C199" t="n">
-        <v>0.002385</v>
+        <v>0.00236</v>
       </c>
       <c r="D199" t="n">
-        <v>0.002385</v>
+        <v>0.00236</v>
       </c>
       <c r="E199" t="n">
         <v>32.239</v>
@@ -3843,10 +3843,10 @@
         <v>9.01e-06</v>
       </c>
       <c r="C200" t="n">
-        <v>0.00243</v>
+        <v>0.00236</v>
       </c>
       <c r="D200" t="n">
-        <v>0.00243</v>
+        <v>0.00236</v>
       </c>
       <c r="E200" t="n">
         <v>32.238</v>
@@ -3860,12 +3860,12 @@
         <v>8.31e-06</v>
       </c>
       <c r="C201" t="n">
-        <v>0.002415</v>
+        <v>0.00236</v>
       </c>
       <c r="D201" t="n">
-        <v>0.002415</v>
-      </c>
-      <c r="E201" s="2" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E201" t="n">
         <v>32.241</v>
       </c>
     </row>
@@ -3877,12 +3877,12 @@
         <v>7.63e-06</v>
       </c>
       <c r="C202" t="n">
-        <v>0.002455</v>
+        <v>0.0024</v>
       </c>
       <c r="D202" t="n">
-        <v>0.002455</v>
-      </c>
-      <c r="E202" s="2" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E202" t="n">
         <v>32.235</v>
       </c>
     </row>
@@ -3894,10 +3894,10 @@
         <v>6.99e-06</v>
       </c>
       <c r="C203" t="n">
-        <v>0.002429999999999999</v>
+        <v>0.00238</v>
       </c>
       <c r="D203" t="n">
-        <v>0.002429999999999999</v>
+        <v>0.00238</v>
       </c>
       <c r="E203" t="n">
         <v>32.238</v>
@@ -3911,10 +3911,10 @@
         <v>6.38e-06</v>
       </c>
       <c r="C204" t="n">
-        <v>0.00245</v>
+        <v>0.00241</v>
       </c>
       <c r="D204" t="n">
-        <v>0.00245</v>
+        <v>0.00241</v>
       </c>
       <c r="E204" s="2" t="n">
         <v>32.243</v>
@@ -3928,12 +3928,12 @@
         <v>5.8e-06</v>
       </c>
       <c r="C205" t="n">
-        <v>0.002445</v>
+        <v>0.00236</v>
       </c>
       <c r="D205" t="n">
-        <v>0.002445</v>
-      </c>
-      <c r="E205" s="3" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E205" s="2" t="n">
         <v>32.245</v>
       </c>
     </row>
@@ -3945,10 +3945,10 @@
         <v>5.25e-06</v>
       </c>
       <c r="C206" t="n">
-        <v>0.00253</v>
+        <v>0.00247</v>
       </c>
       <c r="D206" t="n">
-        <v>0.00253</v>
+        <v>0.00247</v>
       </c>
       <c r="E206" t="n">
         <v>32.241</v>
@@ -3962,10 +3962,10 @@
         <v>4.74e-06</v>
       </c>
       <c r="C207" t="n">
-        <v>0.00242</v>
+        <v>0.00237</v>
       </c>
       <c r="D207" t="n">
-        <v>0.00242</v>
+        <v>0.00237</v>
       </c>
       <c r="E207" t="n">
         <v>32.238</v>
@@ -3979,10 +3979,10 @@
         <v>4.26e-06</v>
       </c>
       <c r="C208" t="n">
-        <v>0.00241</v>
+        <v>0.00234</v>
       </c>
       <c r="D208" t="n">
-        <v>0.00241</v>
+        <v>0.00234</v>
       </c>
       <c r="E208" t="n">
         <v>32.241</v>
@@ -3996,12 +3996,12 @@
         <v>3.81e-06</v>
       </c>
       <c r="C209" t="n">
-        <v>0.00243</v>
+        <v>0.00233</v>
       </c>
       <c r="D209" t="n">
-        <v>0.00243</v>
-      </c>
-      <c r="E209" s="2" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="E209" t="n">
         <v>32.241</v>
       </c>
     </row>
@@ -4013,10 +4013,10 @@
         <v>3.4e-06</v>
       </c>
       <c r="C210" t="n">
-        <v>0.0024</v>
+        <v>0.00239</v>
       </c>
       <c r="D210" t="n">
-        <v>0.0024</v>
+        <v>0.00239</v>
       </c>
       <c r="E210" t="n">
         <v>32.243</v>
@@ -4030,12 +4030,12 @@
         <v>3.02e-06</v>
       </c>
       <c r="C211" t="n">
-        <v>0.00241</v>
+        <v>0.0023</v>
       </c>
       <c r="D211" t="n">
-        <v>0.00241</v>
-      </c>
-      <c r="E211" s="2" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="E211" t="n">
         <v>32.238</v>
       </c>
     </row>
@@ -4047,10 +4047,10 @@
         <v>2.67e-06</v>
       </c>
       <c r="C212" t="n">
-        <v>0.00244</v>
+        <v>0.00237</v>
       </c>
       <c r="D212" t="n">
-        <v>0.00244</v>
+        <v>0.00237</v>
       </c>
       <c r="E212" t="n">
         <v>32.244</v>
@@ -4064,10 +4064,10 @@
         <v>2.35e-06</v>
       </c>
       <c r="C213" t="n">
-        <v>0.002424999999999999</v>
+        <v>0.00235</v>
       </c>
       <c r="D213" t="n">
-        <v>0.002424999999999999</v>
+        <v>0.00235</v>
       </c>
       <c r="E213" t="n">
         <v>32.24</v>
@@ -4081,12 +4081,12 @@
         <v>2.07e-06</v>
       </c>
       <c r="C214" t="n">
-        <v>0.002445</v>
+        <v>0.002379999999999999</v>
       </c>
       <c r="D214" t="n">
-        <v>0.002445</v>
-      </c>
-      <c r="E214" s="2" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="E214" t="n">
         <v>32.243</v>
       </c>
     </row>
@@ -4098,10 +4098,10 @@
         <v>1.82e-06</v>
       </c>
       <c r="C215" t="n">
-        <v>0.002465</v>
+        <v>0.00239</v>
       </c>
       <c r="D215" t="n">
-        <v>0.002465</v>
+        <v>0.00239</v>
       </c>
       <c r="E215" t="n">
         <v>32.241</v>
@@ -4115,10 +4115,10 @@
         <v>1.6e-06</v>
       </c>
       <c r="C216" t="n">
-        <v>0.00244</v>
+        <v>0.00239</v>
       </c>
       <c r="D216" t="n">
-        <v>0.00244</v>
+        <v>0.00239</v>
       </c>
       <c r="E216" t="n">
         <v>32.242</v>
@@ -4132,10 +4132,10 @@
         <v>1.42e-06</v>
       </c>
       <c r="C217" t="n">
-        <v>0.00244</v>
+        <v>0.00235</v>
       </c>
       <c r="D217" t="n">
-        <v>0.00244</v>
+        <v>0.00235</v>
       </c>
       <c r="E217" t="n">
         <v>32.241</v>
@@ -4149,10 +4149,10 @@
         <v>1.27e-06</v>
       </c>
       <c r="C218" t="n">
-        <v>0.00246</v>
+        <v>0.0024</v>
       </c>
       <c r="D218" t="n">
-        <v>0.00246</v>
+        <v>0.0024</v>
       </c>
       <c r="E218" t="n">
         <v>32.241</v>
@@ -4166,10 +4166,10 @@
         <v>1.15e-06</v>
       </c>
       <c r="C219" t="n">
-        <v>0.00248</v>
+        <v>0.00246</v>
       </c>
       <c r="D219" t="n">
-        <v>0.00248</v>
+        <v>0.00246</v>
       </c>
       <c r="E219" t="n">
         <v>32.241</v>
@@ -4183,12 +4183,12 @@
         <v>1.07e-06</v>
       </c>
       <c r="C220" t="n">
-        <v>0.002375</v>
+        <v>0.002379999999999999</v>
       </c>
       <c r="D220" t="n">
-        <v>0.002375</v>
-      </c>
-      <c r="E220" s="2" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="E220" t="n">
         <v>32.242</v>
       </c>
     </row>
@@ -4200,13 +4200,3243 @@
         <v>1.02e-06</v>
       </c>
       <c r="C221" t="n">
-        <v>0.002445</v>
+        <v>0.00242</v>
       </c>
       <c r="D221" t="n">
-        <v>0.002445</v>
+        <v>0.00242</v>
       </c>
       <c r="E221" t="n">
         <v>32.243</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="n">
+        <v>0.000146</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E222" t="n">
+        <v>32.074</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="n">
+        <v>0.000145</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E223" t="n">
+        <v>32.153</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="n">
+        <v>0.000143</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E224" t="n">
+        <v>32.157</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="n">
+        <v>0.000142</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.00245</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0.00245</v>
+      </c>
+      <c r="E225" t="n">
+        <v>32.165</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="n">
+        <v>0.000141</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E226" t="n">
+        <v>32.167</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="n">
+        <v>0.00014</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="E227" t="n">
+        <v>32.171</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="n">
+        <v>0.000138</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E228" t="n">
+        <v>32.182</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="n">
+        <v>0.000137</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E229" t="n">
+        <v>32.157</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="n">
+        <v>0.000136</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0.002419999999999999</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.002419999999999999</v>
+      </c>
+      <c r="E230" t="n">
+        <v>32.162</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="n">
+        <v>0.000135</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="E231" t="n">
+        <v>32.159</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="n">
+        <v>0.000134</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E232" t="n">
+        <v>32.142</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="n">
+        <v>0.000132</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0.00243</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.00243</v>
+      </c>
+      <c r="E233" t="n">
+        <v>32.172</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="n">
+        <v>0.000131</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E234" t="n">
+        <v>32.157</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="n">
+        <v>0.00013</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0.00248</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0.00248</v>
+      </c>
+      <c r="E235" t="n">
+        <v>32.18</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="n">
+        <v>0.000129</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E236" t="n">
+        <v>32.164</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="n">
+        <v>0.000127</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E237" t="n">
+        <v>32.124</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="n">
+        <v>0.000126</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E238" t="n">
+        <v>32.139</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="n">
+        <v>0.000125</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="E239" t="n">
+        <v>32.117</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="n">
+        <v>0.000124</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E240" t="n">
+        <v>32.172</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="n">
+        <v>0.000123</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E241" t="n">
+        <v>32.173</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="n">
+        <v>0.000121</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E242" t="n">
+        <v>32.161</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="n">
+        <v>0.00012</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E243" t="n">
+        <v>32.185</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="n">
+        <v>0.000119</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E244" t="n">
+        <v>32.156</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="n">
+        <v>0.000118</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="E245" t="n">
+        <v>32.187</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="n">
+        <v>0.000117</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E246" t="n">
+        <v>32.16</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="n">
+        <v>0.000115</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E247" t="n">
+        <v>32.179</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="n">
+        <v>0.000114</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E248" t="n">
+        <v>32.172</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="n">
+        <v>0.000113</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E249" t="n">
+        <v>32.217</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="n">
+        <v>0.000112</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="E250" t="n">
+        <v>32.2</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="n">
+        <v>0.000111</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="E251" t="n">
+        <v>32.166</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="n">
+        <v>0.000109</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E252" t="n">
+        <v>32.187</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="n">
+        <v>0.000108</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="E253" t="n">
+        <v>32.189</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="n">
+        <v>0.000107</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E254" t="n">
+        <v>32.173</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="n">
+        <v>0.000106</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E255" t="n">
+        <v>32.19</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="n">
+        <v>0.000105</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="E256" t="n">
+        <v>32.225</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="n">
+        <v>0.000104</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E257" t="n">
+        <v>32.208</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="n">
+        <v>0.000102</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="E258" t="n">
+        <v>32.234</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="n">
+        <v>0.000101</v>
+      </c>
+      <c r="C259" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E259" t="n">
+        <v>32.233</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E260" t="n">
+        <v>32.228</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="n">
+        <v>9.890000000000001e-05</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E261" t="n">
+        <v>32.234</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="n">
+        <v>9.77e-05</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E262" t="n">
+        <v>32.178</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="n">
+        <v>9.66e-05</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0.00245</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0.00245</v>
+      </c>
+      <c r="E263" t="n">
+        <v>32.243</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="n">
+        <v>9.55e-05</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E264" t="n">
+        <v>32.201</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="n">
+        <v>9.43e-05</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E265" s="2" t="n">
+        <v>32.248</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="n">
+        <v>9.32e-05</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="E266" t="n">
+        <v>32.235</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="n">
+        <v>9.21e-05</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E267" t="n">
+        <v>32.198</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="n">
+        <v>9.09e-05</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E268" t="n">
+        <v>32.214</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="n">
+        <v>8.98e-05</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E269" t="n">
+        <v>32.224</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="n">
+        <v>8.87e-05</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="D270" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="E270" t="n">
+        <v>32.245</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="n">
+        <v>8.76e-05</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E271" t="n">
+        <v>32.22</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="n">
+        <v>8.65e-05</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E272" t="n">
+        <v>32.231</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="n">
+        <v>8.54e-05</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E273" t="n">
+        <v>32.233</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="n">
+        <v>8.43e-05</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E274" t="n">
+        <v>32.169</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="n">
+        <v>8.32e-05</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E275" s="2" t="n">
+        <v>32.248</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" t="n">
+        <v>8.21e-05</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.00245</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0.00245</v>
+      </c>
+      <c r="E276" t="n">
+        <v>32.175</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" t="n">
+        <v>8.110000000000001e-05</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E277" t="n">
+        <v>32.184</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" t="n">
+        <v>8.000000000000001e-05</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E278" t="n">
+        <v>32.206</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" t="n">
+        <v>7.889999999999999e-05</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D279" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E279" t="n">
+        <v>32.245</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" t="n">
+        <v>7.779999999999999e-05</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E280" t="n">
+        <v>32.243</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" t="n">
+        <v>7.68e-05</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E281" t="n">
+        <v>32.24</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="n">
+        <v>7.57e-05</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E282" t="n">
+        <v>32.208</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="n">
+        <v>7.47e-05</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D283" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E283" t="n">
+        <v>32.221</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="n">
+        <v>7.36e-05</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="E284" t="n">
+        <v>32.21</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="n">
+        <v>7.26e-05</v>
+      </c>
+      <c r="C285" t="n">
+        <v>0.00223</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0.00223</v>
+      </c>
+      <c r="E285" s="2" t="n">
+        <v>32.251</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="n">
+        <v>7.160000000000001e-05</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D286" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E286" t="n">
+        <v>32.228</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" t="n">
+        <v>7.050000000000001e-05</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0.00247</v>
+      </c>
+      <c r="D287" t="n">
+        <v>0.00247</v>
+      </c>
+      <c r="E287" s="2" t="n">
+        <v>32.252</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" t="n">
+        <v>6.95e-05</v>
+      </c>
+      <c r="C288" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="E288" t="n">
+        <v>32.248</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="n">
+        <v>6.85e-05</v>
+      </c>
+      <c r="C289" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="D289" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="E289" t="n">
+        <v>32.244</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="n">
+        <v>6.75e-05</v>
+      </c>
+      <c r="C290" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D290" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E290" t="n">
+        <v>32.233</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="n">
+        <v>6.65e-05</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D291" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E291" t="n">
+        <v>32.203</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="n">
+        <v>6.550000000000001e-05</v>
+      </c>
+      <c r="C292" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E292" t="n">
+        <v>32.231</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" t="n">
+        <v>6.45e-05</v>
+      </c>
+      <c r="C293" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D293" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E293" t="n">
+        <v>32.237</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" t="n">
+        <v>6.35e-05</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E294" t="n">
+        <v>32.227</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" t="n">
+        <v>6.25e-05</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E295" t="n">
+        <v>32.234</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" t="n">
+        <v>6.15e-05</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="D296" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="E296" t="n">
+        <v>32.238</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" t="n">
+        <v>6.06e-05</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D297" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E297" t="n">
+        <v>32.244</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" t="n">
+        <v>5.96e-05</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="D298" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="E298" t="n">
+        <v>32.249</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="n">
+        <v>5.86e-05</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0.00245</v>
+      </c>
+      <c r="D299" t="n">
+        <v>0.00245</v>
+      </c>
+      <c r="E299" s="2" t="n">
+        <v>32.256</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="n">
+        <v>5.77e-05</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D300" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E300" t="n">
+        <v>32.246</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" t="n">
+        <v>5.67e-05</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="D301" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E301" s="2" t="n">
+        <v>32.256</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" t="n">
+        <v>5.58e-05</v>
+      </c>
+      <c r="C302" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E302" t="n">
+        <v>32.239</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" t="n">
+        <v>5.49e-05</v>
+      </c>
+      <c r="C303" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D303" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E303" t="n">
+        <v>32.247</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" t="n">
+        <v>5.39e-05</v>
+      </c>
+      <c r="C304" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E304" t="n">
+        <v>32.239</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" t="n">
+        <v>5.3e-05</v>
+      </c>
+      <c r="C305" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D305" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E305" t="n">
+        <v>32.247</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" t="n">
+        <v>5.21e-05</v>
+      </c>
+      <c r="C306" t="n">
+        <v>0.00246</v>
+      </c>
+      <c r="D306" t="n">
+        <v>0.00246</v>
+      </c>
+      <c r="E306" t="n">
+        <v>32.239</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" t="n">
+        <v>5.12e-05</v>
+      </c>
+      <c r="C307" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="D307" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E307" t="n">
+        <v>32.241</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" t="n">
+        <v>5.03e-05</v>
+      </c>
+      <c r="C308" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D308" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E308" t="n">
+        <v>32.253</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" t="n">
+        <v>4.94e-05</v>
+      </c>
+      <c r="C309" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="D309" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="E309" t="n">
+        <v>32.255</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" t="n">
+        <v>4.85e-05</v>
+      </c>
+      <c r="C310" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D310" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E310" s="2" t="n">
+        <v>32.258</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" t="n">
+        <v>4.76e-05</v>
+      </c>
+      <c r="C311" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D311" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E311" t="n">
+        <v>32.249</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" t="n">
+        <v>4.68e-05</v>
+      </c>
+      <c r="C312" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D312" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E312" s="2" t="n">
+        <v>32.274</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" t="n">
+        <v>4.59e-05</v>
+      </c>
+      <c r="C313" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="D313" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="E313" t="n">
+        <v>32.262</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" t="n">
+        <v>4.5e-05</v>
+      </c>
+      <c r="C314" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="D314" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="E314" t="n">
+        <v>32.256</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" t="n">
+        <v>4.42e-05</v>
+      </c>
+      <c r="C315" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D315" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E315" t="n">
+        <v>32.256</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" t="n">
+        <v>4.33e-05</v>
+      </c>
+      <c r="C316" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E316" t="n">
+        <v>32.249</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" t="n">
+        <v>4.25e-05</v>
+      </c>
+      <c r="C317" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E317" t="n">
+        <v>32.227</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" t="n">
+        <v>4.17e-05</v>
+      </c>
+      <c r="C318" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D318" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E318" t="n">
+        <v>32.269</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" t="n">
+        <v>4.08e-05</v>
+      </c>
+      <c r="C319" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D319" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E319" t="n">
+        <v>32.263</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" t="n">
+        <v>4e-05</v>
+      </c>
+      <c r="C320" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D320" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E320" t="n">
+        <v>32.273</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" t="n">
+        <v>3.92e-05</v>
+      </c>
+      <c r="C321" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D321" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E321" t="n">
+        <v>32.273</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" t="n">
+        <v>3.84e-05</v>
+      </c>
+      <c r="C322" t="n">
+        <v>0.00227</v>
+      </c>
+      <c r="D322" t="n">
+        <v>0.00227</v>
+      </c>
+      <c r="E322" t="n">
+        <v>32.26</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" t="n">
+        <v>3.76e-05</v>
+      </c>
+      <c r="C323" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D323" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E323" t="n">
+        <v>32.26</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" t="n">
+        <v>3.68e-05</v>
+      </c>
+      <c r="C324" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="D324" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="E324" s="2" t="n">
+        <v>32.275</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" t="n">
+        <v>3.6e-05</v>
+      </c>
+      <c r="C325" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D325" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E325" t="n">
+        <v>32.266</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" t="n">
+        <v>3.53e-05</v>
+      </c>
+      <c r="C326" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D326" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E326" s="2" t="n">
+        <v>32.278</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" t="n">
+        <v>3.45e-05</v>
+      </c>
+      <c r="C327" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D327" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E327" t="n">
+        <v>32.262</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" t="n">
+        <v>3.38e-05</v>
+      </c>
+      <c r="C328" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D328" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E328" t="n">
+        <v>32.273</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" t="n">
+        <v>3.3e-05</v>
+      </c>
+      <c r="C329" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D329" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E329" t="n">
+        <v>32.27</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" t="n">
+        <v>3.23e-05</v>
+      </c>
+      <c r="C330" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D330" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E330" s="2" t="n">
+        <v>32.287</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" t="n">
+        <v>3.15e-05</v>
+      </c>
+      <c r="C331" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D331" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E331" t="n">
+        <v>32.271</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" t="n">
+        <v>3.08e-05</v>
+      </c>
+      <c r="C332" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="D332" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="E332" t="n">
+        <v>32.276</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" t="n">
+        <v>3.01e-05</v>
+      </c>
+      <c r="C333" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D333" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E333" t="n">
+        <v>32.256</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" t="n">
+        <v>2.94e-05</v>
+      </c>
+      <c r="C334" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D334" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E334" t="n">
+        <v>32.266</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" t="n">
+        <v>2.87e-05</v>
+      </c>
+      <c r="C335" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="D335" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="E335" s="2" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" t="n">
+        <v>2.8e-05</v>
+      </c>
+      <c r="C336" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D336" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E336" t="n">
+        <v>32.281</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" t="n">
+        <v>2.73e-05</v>
+      </c>
+      <c r="C337" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D337" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E337" t="n">
+        <v>32.27</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" t="n">
+        <v>2.66e-05</v>
+      </c>
+      <c r="C338" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D338" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E338" t="n">
+        <v>32.278</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" t="n">
+        <v>2.6e-05</v>
+      </c>
+      <c r="C339" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="D339" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="E339" t="n">
+        <v>32.29</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" t="n">
+        <v>2.53e-05</v>
+      </c>
+      <c r="C340" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="D340" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="E340" t="n">
+        <v>32.285</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" t="n">
+        <v>2.46e-05</v>
+      </c>
+      <c r="C341" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="D341" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="E341" t="n">
+        <v>32.282</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" t="n">
+        <v>2.4e-05</v>
+      </c>
+      <c r="C342" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D342" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E342" t="n">
+        <v>32.275</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" t="n">
+        <v>2.34e-05</v>
+      </c>
+      <c r="C343" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E343" t="n">
+        <v>32.291</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" t="n">
+        <v>2.27e-05</v>
+      </c>
+      <c r="C344" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="D344" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="E344" t="n">
+        <v>32.289</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" t="n">
+        <v>2.21e-05</v>
+      </c>
+      <c r="C345" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="D345" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="E345" t="n">
+        <v>32.276</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" t="n">
+        <v>2.15e-05</v>
+      </c>
+      <c r="C346" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D346" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E346" t="n">
+        <v>32.272</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" t="n">
+        <v>2.09e-05</v>
+      </c>
+      <c r="C347" t="n">
+        <v>0.002429999999999999</v>
+      </c>
+      <c r="D347" t="n">
+        <v>0.002429999999999999</v>
+      </c>
+      <c r="E347" t="n">
+        <v>32.27</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" t="n">
+        <v>2.03e-05</v>
+      </c>
+      <c r="C348" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D348" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E348" t="n">
+        <v>32.277</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" t="n">
+        <v>1.97e-05</v>
+      </c>
+      <c r="C349" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="D349" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="E349" t="n">
+        <v>32.277</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" t="n">
+        <v>1.91e-05</v>
+      </c>
+      <c r="C350" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D350" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E350" t="n">
+        <v>32.278</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" t="n">
+        <v>1.86e-05</v>
+      </c>
+      <c r="C351" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D351" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E351" t="n">
+        <v>32.278</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" t="n">
+        <v>1.8e-05</v>
+      </c>
+      <c r="C352" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="D352" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E352" t="n">
+        <v>32.28</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" t="n">
+        <v>1.74e-05</v>
+      </c>
+      <c r="C353" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="D353" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="E353" t="n">
+        <v>32.277</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" t="n">
+        <v>1.69e-05</v>
+      </c>
+      <c r="C354" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D354" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E354" t="n">
+        <v>32.277</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" t="n">
+        <v>1.64e-05</v>
+      </c>
+      <c r="C355" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E355" t="n">
+        <v>32.287</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" t="n">
+        <v>1.58e-05</v>
+      </c>
+      <c r="C356" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="D356" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="E356" t="n">
+        <v>32.28</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" t="n">
+        <v>1.53e-05</v>
+      </c>
+      <c r="C357" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="D357" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="E357" t="n">
+        <v>32.285</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" t="n">
+        <v>1.48e-05</v>
+      </c>
+      <c r="C358" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="D358" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E358" t="n">
+        <v>32.283</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" t="n">
+        <v>1.43e-05</v>
+      </c>
+      <c r="C359" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D359" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E359" t="n">
+        <v>32.277</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" t="n">
+        <v>1.38e-05</v>
+      </c>
+      <c r="C360" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="D360" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="E360" t="n">
+        <v>32.29</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" t="n">
+        <v>1.33e-05</v>
+      </c>
+      <c r="C361" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D361" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E361" t="n">
+        <v>32.279</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" t="n">
+        <v>1.29e-05</v>
+      </c>
+      <c r="C362" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="D362" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E362" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" t="n">
+        <v>1.24e-05</v>
+      </c>
+      <c r="C363" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D363" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E363" t="n">
+        <v>32.289</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" t="n">
+        <v>1.19e-05</v>
+      </c>
+      <c r="C364" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="D364" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="E364" t="n">
+        <v>32.29</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" t="n">
+        <v>1.15e-05</v>
+      </c>
+      <c r="C365" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="D365" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="E365" t="n">
+        <v>32.289</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" t="n">
+        <v>1.11e-05</v>
+      </c>
+      <c r="C366" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D366" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E366" t="n">
+        <v>32.288</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" t="n">
+        <v>1.06e-05</v>
+      </c>
+      <c r="C367" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D367" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E367" t="n">
+        <v>32.288</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" t="n">
+        <v>1.02e-05</v>
+      </c>
+      <c r="C368" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D368" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E368" t="n">
+        <v>32.289</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" t="n">
+        <v>9.809999999999999e-06</v>
+      </c>
+      <c r="C369" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D369" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E369" t="n">
+        <v>32.285</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" t="n">
+        <v>9.4e-06</v>
+      </c>
+      <c r="C370" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D370" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E370" t="n">
+        <v>32.286</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" t="n">
+        <v>9.01e-06</v>
+      </c>
+      <c r="C371" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="D371" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="E371" t="n">
+        <v>32.282</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" t="n">
+        <v>8.63e-06</v>
+      </c>
+      <c r="C372" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="D372" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="E372" t="n">
+        <v>32.282</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" t="n">
+        <v>8.260000000000001e-06</v>
+      </c>
+      <c r="C373" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="D373" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="E373" t="n">
+        <v>32.283</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" t="n">
+        <v>7.890000000000001e-06</v>
+      </c>
+      <c r="C374" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="D374" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="E374" t="n">
+        <v>32.28</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" t="n">
+        <v>7.54e-06</v>
+      </c>
+      <c r="C375" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D375" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E375" t="n">
+        <v>32.287</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" t="n">
+        <v>7.19e-06</v>
+      </c>
+      <c r="C376" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D376" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E376" s="2" t="n">
+        <v>32.294</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" t="n">
+        <v>6.85e-06</v>
+      </c>
+      <c r="C377" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="D377" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="E377" t="n">
+        <v>32.293</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" t="n">
+        <v>6.52e-06</v>
+      </c>
+      <c r="C378" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="D378" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="E378" t="n">
+        <v>32.289</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" t="n">
+        <v>6.21e-06</v>
+      </c>
+      <c r="C379" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="D379" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="E379" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" t="n">
+        <v>5.9e-06</v>
+      </c>
+      <c r="C380" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="E380" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" t="n">
+        <v>5.6e-06</v>
+      </c>
+      <c r="C381" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D381" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E381" s="2" t="n">
+        <v>32.298</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" t="n">
+        <v>5.31e-06</v>
+      </c>
+      <c r="C382" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="D382" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="E382" t="n">
+        <v>32.293</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" t="n">
+        <v>5.03e-06</v>
+      </c>
+      <c r="C383" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="D383" t="n">
+        <v>0.00238</v>
+      </c>
+      <c r="E383" t="n">
+        <v>32.294</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="n">
+        <v>383</v>
+      </c>
+      <c r="B384" t="n">
+        <v>4.75e-06</v>
+      </c>
+      <c r="C384" t="n">
+        <v>0.002429999999999999</v>
+      </c>
+      <c r="D384" t="n">
+        <v>0.002429999999999999</v>
+      </c>
+      <c r="E384" t="n">
+        <v>32.294</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="n">
+        <v>384</v>
+      </c>
+      <c r="B385" t="n">
+        <v>4.49e-06</v>
+      </c>
+      <c r="C385" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D385" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E385" t="n">
+        <v>32.294</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="n">
+        <v>385</v>
+      </c>
+      <c r="B386" t="n">
+        <v>4.24e-06</v>
+      </c>
+      <c r="C386" t="n">
+        <v>0.00225</v>
+      </c>
+      <c r="D386" t="n">
+        <v>0.00225</v>
+      </c>
+      <c r="E386" t="n">
+        <v>32.293</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="n">
+        <v>386</v>
+      </c>
+      <c r="B387" t="n">
+        <v>3.99e-06</v>
+      </c>
+      <c r="C387" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D387" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E387" t="n">
+        <v>32.291</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="n">
+        <v>387</v>
+      </c>
+      <c r="B388" t="n">
+        <v>3.76e-06</v>
+      </c>
+      <c r="C388" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D388" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E388" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="n">
+        <v>388</v>
+      </c>
+      <c r="B389" t="n">
+        <v>3.54e-06</v>
+      </c>
+      <c r="C389" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="D389" t="n">
+        <v>0.00229</v>
+      </c>
+      <c r="E389" t="n">
+        <v>32.29</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="n">
+        <v>389</v>
+      </c>
+      <c r="B390" t="n">
+        <v>3.32e-06</v>
+      </c>
+      <c r="C390" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D390" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E390" s="3" t="n">
+        <v>32.299</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="n">
+        <v>390</v>
+      </c>
+      <c r="B391" t="n">
+        <v>3.11e-06</v>
+      </c>
+      <c r="C391" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="D391" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="E391" t="n">
+        <v>32.294</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="n">
+        <v>391</v>
+      </c>
+      <c r="B392" t="n">
+        <v>2.92e-06</v>
+      </c>
+      <c r="C392" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="D392" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="E392" t="n">
+        <v>32.294</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="n">
+        <v>392</v>
+      </c>
+      <c r="B393" t="n">
+        <v>2.73e-06</v>
+      </c>
+      <c r="C393" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="D393" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E393" t="n">
+        <v>32.291</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="n">
+        <v>393</v>
+      </c>
+      <c r="B394" t="n">
+        <v>2.55e-06</v>
+      </c>
+      <c r="C394" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D394" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E394" t="n">
+        <v>32.293</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="n">
+        <v>394</v>
+      </c>
+      <c r="B395" t="n">
+        <v>2.39e-06</v>
+      </c>
+      <c r="C395" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="D395" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="E395" t="n">
+        <v>32.29</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="n">
+        <v>395</v>
+      </c>
+      <c r="B396" t="n">
+        <v>2.23e-06</v>
+      </c>
+      <c r="C396" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="D396" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="E396" t="n">
+        <v>32.29</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="n">
+        <v>396</v>
+      </c>
+      <c r="B397" t="n">
+        <v>2.08e-06</v>
+      </c>
+      <c r="C397" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D397" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E397" t="n">
+        <v>32.294</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="n">
+        <v>397</v>
+      </c>
+      <c r="B398" t="n">
+        <v>1.94e-06</v>
+      </c>
+      <c r="C398" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="D398" t="n">
+        <v>0.00236</v>
+      </c>
+      <c r="E398" t="n">
+        <v>32.294</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="n">
+        <v>398</v>
+      </c>
+      <c r="B399" t="n">
+        <v>1.81e-06</v>
+      </c>
+      <c r="C399" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="D399" t="n">
+        <v>0.00235</v>
+      </c>
+      <c r="E399" t="n">
+        <v>32.291</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="n">
+        <v>399</v>
+      </c>
+      <c r="B400" t="n">
+        <v>1.69e-06</v>
+      </c>
+      <c r="C400" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="D400" t="n">
+        <v>0.002379999999999999</v>
+      </c>
+      <c r="E400" t="n">
+        <v>32.293</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="n">
+        <v>400</v>
+      </c>
+      <c r="B401" t="n">
+        <v>1.58e-06</v>
+      </c>
+      <c r="C401" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="D401" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E401" t="n">
+        <v>32.295</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="n">
+        <v>401</v>
+      </c>
+      <c r="B402" t="n">
+        <v>1.48e-06</v>
+      </c>
+      <c r="C402" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="D402" t="n">
+        <v>0.00244</v>
+      </c>
+      <c r="E402" t="n">
+        <v>32.295</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="n">
+        <v>402</v>
+      </c>
+      <c r="B403" t="n">
+        <v>1.39e-06</v>
+      </c>
+      <c r="C403" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="D403" t="n">
+        <v>0.00233</v>
+      </c>
+      <c r="E403" t="n">
+        <v>32.294</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="n">
+        <v>403</v>
+      </c>
+      <c r="B404" t="n">
+        <v>1.31e-06</v>
+      </c>
+      <c r="C404" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="D404" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="E404" t="n">
+        <v>32.296</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="n">
+        <v>404</v>
+      </c>
+      <c r="B405" t="n">
+        <v>1.24e-06</v>
+      </c>
+      <c r="C405" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="D405" t="n">
+        <v>0.00239</v>
+      </c>
+      <c r="E405" t="n">
+        <v>32.293</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="n">
+        <v>405</v>
+      </c>
+      <c r="B406" t="n">
+        <v>1.17e-06</v>
+      </c>
+      <c r="C406" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="D406" t="n">
+        <v>0.00228</v>
+      </c>
+      <c r="E406" t="n">
+        <v>32.293</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="n">
+        <v>406</v>
+      </c>
+      <c r="B407" t="n">
+        <v>1.12e-06</v>
+      </c>
+      <c r="C407" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="D407" t="n">
+        <v>0.00234</v>
+      </c>
+      <c r="E407" t="n">
+        <v>32.293</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" t="n">
+        <v>1.08e-06</v>
+      </c>
+      <c r="C408" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="D408" t="n">
+        <v>0.00231</v>
+      </c>
+      <c r="E408" t="n">
+        <v>32.292</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" t="n">
+        <v>1.04e-06</v>
+      </c>
+      <c r="C409" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="D409" t="n">
+        <v>0.00232</v>
+      </c>
+      <c r="E409" t="n">
+        <v>32.295</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" t="n">
+        <v>1.02e-06</v>
+      </c>
+      <c r="C410" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="D410" t="n">
+        <v>0.00241</v>
+      </c>
+      <c r="E410" t="n">
+        <v>32.294</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="C411" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="D411" t="n">
+        <v>0.00237</v>
+      </c>
+      <c r="E411" t="n">
+        <v>32.294</v>
       </c>
     </row>
   </sheetData>
